--- a/Code/Jupiter/Connect4/EVAL_PPO_results.xlsx
+++ b/Code/Jupiter/Connect4/EVAL_PPO_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>TRAINING_SESSION</t>
   </si>
@@ -185,6 +185,12 @@
   </si>
   <si>
     <t>PPO_404</t>
+  </si>
+  <si>
+    <t>PPO-1000-CUR-Focused_POP_SP-PPO_404 - at-2026-01-21 07-32-48</t>
+  </si>
+  <si>
+    <t>PPO_405</t>
   </si>
 </sst>
 </file>
@@ -542,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -2718,6 +2724,112 @@
         <v>0.5896232109822206</v>
       </c>
     </row>
+    <row r="42" spans="1:17">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42">
+        <v>0.020262</v>
+      </c>
+      <c r="C42">
+        <v>1000</v>
+      </c>
+      <c r="D42">
+        <v>0.995</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>0.5</v>
+      </c>
+      <c r="G42">
+        <v>0.79</v>
+      </c>
+      <c r="H42">
+        <v>0.28</v>
+      </c>
+      <c r="I42">
+        <v>0.5</v>
+      </c>
+      <c r="J42">
+        <v>0.5</v>
+      </c>
+      <c r="K42">
+        <v>0.5</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0.5</v>
+      </c>
+      <c r="N42">
+        <v>0.5</v>
+      </c>
+      <c r="O42">
+        <v>0.5</v>
+      </c>
+      <c r="P42">
+        <v>0.5</v>
+      </c>
+      <c r="Q42">
+        <v>0.484202339181929</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43">
+        <v>0.019964</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0.995</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>0.5</v>
+      </c>
+      <c r="G43">
+        <v>0.77</v>
+      </c>
+      <c r="H43">
+        <v>0.23</v>
+      </c>
+      <c r="I43">
+        <v>0.5</v>
+      </c>
+      <c r="J43">
+        <v>0.5</v>
+      </c>
+      <c r="K43">
+        <v>0.5</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0.5</v>
+      </c>
+      <c r="N43">
+        <v>0.5</v>
+      </c>
+      <c r="O43">
+        <v>0.5</v>
+      </c>
+      <c r="P43">
+        <v>0.5</v>
+      </c>
+      <c r="Q43">
+        <v>0.483490164565591</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Code/Jupiter/Connect4/EVAL_PPO_results.xlsx
+++ b/Code/Jupiter/Connect4/EVAL_PPO_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>TRAINING_SESSION</t>
   </si>
@@ -191,6 +191,63 @@
   </si>
   <si>
     <t>PPO_405</t>
+  </si>
+  <si>
+    <t>PPO-1000-CUR-Focused_POP_SP-PPO_405 - at-2026-01-21 08-24-19</t>
+  </si>
+  <si>
+    <t>PPO-2000-CUR-Finale_B-PPO_405 - at-2026-01-21 08-57-41</t>
+  </si>
+  <si>
+    <t>PPO_406</t>
+  </si>
+  <si>
+    <t>PPO-500-EXP-EXPLORE-PPO_404 - at-2026-01-21 10-32-47</t>
+  </si>
+  <si>
+    <t>PPO-500-EXP-EXPLORE-PPO_404 - at-2026-01-21 10-56-28</t>
+  </si>
+  <si>
+    <t>PPO-500-EXP-EXPLORE-PPO_404 - at-2026-01-21 11-09-11</t>
+  </si>
+  <si>
+    <t>PPO-500-EXP-EXPLORE-PPO_404 - at-2026-01-21 11-25-57</t>
+  </si>
+  <si>
+    <t>EXP_1</t>
+  </si>
+  <si>
+    <t>PPO-500-EXP-EXPLORE-PPO_404 - at-2026-01-21 11-47-37</t>
+  </si>
+  <si>
+    <t>PPO-500-EXP-EXPLORE-PPO_404 - at-2026-01-21 12-13-50</t>
+  </si>
+  <si>
+    <t>PPO-500-EXP-EXPLORE-PPO_404 - at-2026-01-21 12-28-27</t>
+  </si>
+  <si>
+    <t>PPO-500-EXP-EXPLORE-PPO_404 - at-2026-01-21 12-56-14</t>
+  </si>
+  <si>
+    <t>PPO-500-EXP-EXPLORE-PPO_404 - at-2026-01-21 13-12-29</t>
+  </si>
+  <si>
+    <t>PPO-500-EXP-EXPLORE-PPO_404 - at-2026-01-21 13-31-07</t>
+  </si>
+  <si>
+    <t>PPO-1000-FOC-Focused_POP_SP-PPO_404 - at-2026-01-21 13-45-00</t>
+  </si>
+  <si>
+    <t>PPO-2700-FOC-Finale_B-BASE_4 - at-2026-01-21 14-39-00</t>
+  </si>
+  <si>
+    <t>PPO_407</t>
+  </si>
+  <si>
+    <t>PPO-2700-FOC-Finale_B-PPO_404 - at-2026-01-21 16-24-52</t>
+  </si>
+  <si>
+    <t>PPO_408</t>
   </si>
 </sst>
 </file>
@@ -548,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -2830,6 +2887,1013 @@
         <v>0.483490164565591</v>
       </c>
     </row>
+    <row r="44" spans="1:17">
+      <c r="A44" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44">
+        <v>0.016667</v>
+      </c>
+      <c r="C44">
+        <v>1000</v>
+      </c>
+      <c r="D44">
+        <v>0.99</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>0.5</v>
+      </c>
+      <c r="G44">
+        <v>0.21</v>
+      </c>
+      <c r="H44">
+        <v>0.28</v>
+      </c>
+      <c r="I44">
+        <v>0.5</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0.5</v>
+      </c>
+      <c r="M44">
+        <v>0.5</v>
+      </c>
+      <c r="N44">
+        <v>0.5</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0.1360522933541178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45">
+        <v>0.020397</v>
+      </c>
+      <c r="C45">
+        <v>2000</v>
+      </c>
+      <c r="D45">
+        <v>0.99</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>0.5</v>
+      </c>
+      <c r="G45">
+        <v>0.73</v>
+      </c>
+      <c r="H45">
+        <v>0.5</v>
+      </c>
+      <c r="I45">
+        <v>0.5</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>0.5</v>
+      </c>
+      <c r="L45">
+        <v>0.5</v>
+      </c>
+      <c r="M45">
+        <v>0.5</v>
+      </c>
+      <c r="N45">
+        <v>0.5</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0.5</v>
+      </c>
+      <c r="Q45">
+        <v>0.4038280197975537</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46">
+        <v>0.019692</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>0.5</v>
+      </c>
+      <c r="G46">
+        <v>0.74</v>
+      </c>
+      <c r="H46">
+        <v>0.5</v>
+      </c>
+      <c r="I46">
+        <v>0.5</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <v>0.5</v>
+      </c>
+      <c r="L46">
+        <v>0.5</v>
+      </c>
+      <c r="M46">
+        <v>0.5</v>
+      </c>
+      <c r="N46">
+        <v>0.5</v>
+      </c>
+      <c r="O46">
+        <v>0.5</v>
+      </c>
+      <c r="P46">
+        <v>0.5</v>
+      </c>
+      <c r="Q46">
+        <v>0.5184080181784886</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47">
+        <v>0.017679</v>
+      </c>
+      <c r="C47">
+        <v>500</v>
+      </c>
+      <c r="D47">
+        <v>0.995</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>0.5</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>0.19</v>
+      </c>
+      <c r="I47">
+        <v>0.29</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>0.5</v>
+      </c>
+      <c r="L47">
+        <v>0.5</v>
+      </c>
+      <c r="M47">
+        <v>0.5</v>
+      </c>
+      <c r="N47">
+        <v>0.5</v>
+      </c>
+      <c r="O47">
+        <v>0.5</v>
+      </c>
+      <c r="P47">
+        <v>0.5</v>
+      </c>
+      <c r="Q47">
+        <v>0.5137458744440423</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48">
+        <v>0.016894</v>
+      </c>
+      <c r="C48">
+        <v>500</v>
+      </c>
+      <c r="D48">
+        <v>0.995</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>0.5</v>
+      </c>
+      <c r="G48">
+        <v>0.2</v>
+      </c>
+      <c r="H48">
+        <v>0.27</v>
+      </c>
+      <c r="I48">
+        <v>0.5</v>
+      </c>
+      <c r="J48">
+        <v>0.5</v>
+      </c>
+      <c r="K48">
+        <v>0.5</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0.5</v>
+      </c>
+      <c r="N48">
+        <v>0.5</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0.1406675918249116</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49">
+        <v>0.016762</v>
+      </c>
+      <c r="C49">
+        <v>500</v>
+      </c>
+      <c r="D49">
+        <v>0.99</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>0.5</v>
+      </c>
+      <c r="G49">
+        <v>0.75</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0.5</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>0.5</v>
+      </c>
+      <c r="L49">
+        <v>0.5</v>
+      </c>
+      <c r="M49">
+        <v>0.5</v>
+      </c>
+      <c r="N49">
+        <v>0.5</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0.1741362266153563</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50">
+        <v>0.020132</v>
+      </c>
+      <c r="C50">
+        <v>500</v>
+      </c>
+      <c r="D50">
+        <v>0.995</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>0.5</v>
+      </c>
+      <c r="G50">
+        <v>0.29</v>
+      </c>
+      <c r="H50">
+        <v>0.28</v>
+      </c>
+      <c r="I50">
+        <v>0.5</v>
+      </c>
+      <c r="J50">
+        <v>0.5</v>
+      </c>
+      <c r="K50">
+        <v>0.5</v>
+      </c>
+      <c r="L50">
+        <v>0.5</v>
+      </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0.2509504684265837</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51">
+        <v>0.02188</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0.995</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>0.5</v>
+      </c>
+      <c r="G51">
+        <v>0.22</v>
+      </c>
+      <c r="H51">
+        <v>0.22</v>
+      </c>
+      <c r="I51">
+        <v>0.5</v>
+      </c>
+      <c r="J51">
+        <v>0.5</v>
+      </c>
+      <c r="K51">
+        <v>0.5</v>
+      </c>
+      <c r="L51">
+        <v>0.5</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0.2497318585275165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52">
+        <v>0.018348</v>
+      </c>
+      <c r="C52">
+        <v>500</v>
+      </c>
+      <c r="D52">
+        <v>0.985</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>0.5</v>
+      </c>
+      <c r="G52">
+        <v>0.76</v>
+      </c>
+      <c r="H52">
+        <v>0.23</v>
+      </c>
+      <c r="I52">
+        <v>0.5</v>
+      </c>
+      <c r="J52">
+        <v>0.5</v>
+      </c>
+      <c r="K52">
+        <v>0.5</v>
+      </c>
+      <c r="L52">
+        <v>0.5</v>
+      </c>
+      <c r="M52">
+        <v>0.5</v>
+      </c>
+      <c r="N52">
+        <v>0.5</v>
+      </c>
+      <c r="O52">
+        <v>0.5</v>
+      </c>
+      <c r="P52">
+        <v>0.5</v>
+      </c>
+      <c r="Q52">
+        <v>0.5046336567497928</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53">
+        <v>0.018776</v>
+      </c>
+      <c r="C53">
+        <v>500</v>
+      </c>
+      <c r="D53">
+        <v>0.985</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>0.5</v>
+      </c>
+      <c r="G53">
+        <v>0.76</v>
+      </c>
+      <c r="H53">
+        <v>0.21</v>
+      </c>
+      <c r="I53">
+        <v>0.5</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>0.5</v>
+      </c>
+      <c r="L53">
+        <v>0.5</v>
+      </c>
+      <c r="M53">
+        <v>0.5</v>
+      </c>
+      <c r="N53">
+        <v>0.5</v>
+      </c>
+      <c r="O53">
+        <v>0.5</v>
+      </c>
+      <c r="P53">
+        <v>0.5</v>
+      </c>
+      <c r="Q53">
+        <v>0.5152687976871066</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54">
+        <v>0.017361</v>
+      </c>
+      <c r="C54">
+        <v>500</v>
+      </c>
+      <c r="D54">
+        <v>0.995</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>0.5</v>
+      </c>
+      <c r="G54">
+        <v>0.74</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0.5</v>
+      </c>
+      <c r="J54">
+        <v>0.5</v>
+      </c>
+      <c r="K54">
+        <v>0.5</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>0.5</v>
+      </c>
+      <c r="N54">
+        <v>0.5</v>
+      </c>
+      <c r="O54">
+        <v>0.5</v>
+      </c>
+      <c r="P54">
+        <v>0.5</v>
+      </c>
+      <c r="Q54">
+        <v>0.5232630594947315</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55">
+        <v>0.017102</v>
+      </c>
+      <c r="C55">
+        <v>500</v>
+      </c>
+      <c r="D55">
+        <v>0.98</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>0.5</v>
+      </c>
+      <c r="G55">
+        <v>0.71</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0.26</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>0.5</v>
+      </c>
+      <c r="L55">
+        <v>0.5</v>
+      </c>
+      <c r="M55">
+        <v>0.5</v>
+      </c>
+      <c r="N55">
+        <v>0.5</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0.1700408834406432</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56">
+        <v>0.016652</v>
+      </c>
+      <c r="C56">
+        <v>500</v>
+      </c>
+      <c r="D56">
+        <v>0.995</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>0.5</v>
+      </c>
+      <c r="G56">
+        <v>0.83</v>
+      </c>
+      <c r="H56">
+        <v>0.28</v>
+      </c>
+      <c r="I56">
+        <v>0.5</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>0.5</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>0.5</v>
+      </c>
+      <c r="N56">
+        <v>0.5</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0.1991785922150338</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57">
+        <v>0.016534</v>
+      </c>
+      <c r="C57">
+        <v>500</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>0.5</v>
+      </c>
+      <c r="G57">
+        <v>0.71</v>
+      </c>
+      <c r="H57">
+        <v>0.24</v>
+      </c>
+      <c r="I57">
+        <v>0.3</v>
+      </c>
+      <c r="J57">
+        <v>0.5</v>
+      </c>
+      <c r="K57">
+        <v>0.5</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0.5</v>
+      </c>
+      <c r="N57">
+        <v>0.5</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0.1412972446206263</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="A58" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58">
+        <v>0.024052</v>
+      </c>
+      <c r="C58">
+        <v>1000</v>
+      </c>
+      <c r="D58">
+        <v>0.995</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>0.27</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0.5</v>
+      </c>
+      <c r="J58">
+        <v>0.5</v>
+      </c>
+      <c r="K58">
+        <v>0.5</v>
+      </c>
+      <c r="L58">
+        <v>0.5</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0.5</v>
+      </c>
+      <c r="Q58">
+        <v>0.4748272993445866</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
+      <c r="A59" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59">
+        <v>0.021264</v>
+      </c>
+      <c r="C59">
+        <v>2700</v>
+      </c>
+      <c r="D59">
+        <v>0.99</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>0.24</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0.5</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <v>0.5</v>
+      </c>
+      <c r="N59">
+        <v>0.5</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0.1876917808714515</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17">
+      <c r="A60" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60">
+        <v>0.021346</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0.995</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>0.5</v>
+      </c>
+      <c r="G60">
+        <v>0.33</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0.5</v>
+      </c>
+      <c r="J60">
+        <v>0.5</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60">
+        <v>0.5</v>
+      </c>
+      <c r="N60">
+        <v>0.5</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0.1964628330113982</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="A61" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61">
+        <v>0.021794</v>
+      </c>
+      <c r="C61">
+        <v>2700</v>
+      </c>
+      <c r="D61">
+        <v>0.99</v>
+      </c>
+      <c r="E61">
+        <v>0.5</v>
+      </c>
+      <c r="F61">
+        <v>0.5</v>
+      </c>
+      <c r="G61">
+        <v>0.17</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0.22</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0.3</v>
+      </c>
+      <c r="L61">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M61">
+        <v>0.5</v>
+      </c>
+      <c r="N61">
+        <v>0.5</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0.1274916680886408</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="A62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62">
+        <v>0.017468</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0.985</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0.23</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0.9</v>
+      </c>
+      <c r="N62">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0.173629112829928</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Code/Jupiter/Connect4/EVAL_PPO_results.xlsx
+++ b/Code/Jupiter/Connect4/EVAL_PPO_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="343">
   <si>
     <t>TRAINING_SESSION</t>
   </si>
@@ -935,6 +935,114 @@
   </si>
   <si>
     <t>SOUP_1</t>
+  </si>
+  <si>
+    <t>PPO_847</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_845 - at-2026-04-17 10-56-03</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_845 - at-2026-04-17 14-04-13</t>
+  </si>
+  <si>
+    <t>PPO_848</t>
+  </si>
+  <si>
+    <t>SOUP_2</t>
+  </si>
+  <si>
+    <t>SOUP_3</t>
+  </si>
+  <si>
+    <t>SOUP_4</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_909 - at-2026-04-17 19-24-23</t>
+  </si>
+  <si>
+    <t>PPO_915</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-SOUP_4 - at-2026-04-17 22-33-55</t>
+  </si>
+  <si>
+    <t>PPO_S1</t>
+  </si>
+  <si>
+    <t>SOUP_5</t>
+  </si>
+  <si>
+    <t>SOUP_6</t>
+  </si>
+  <si>
+    <t>SOUP_7</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-SOUP_1 - at-2026-04-18 07-16-34</t>
+  </si>
+  <si>
+    <t>PPO_S2</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_817 - at-2026-04-18 10-30-36</t>
+  </si>
+  <si>
+    <t>PPO_849</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_832 - at-2026-04-18 15-47-05</t>
+  </si>
+  <si>
+    <t>SOUP_9</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_836 - at-2026-04-18 22-01-01</t>
+  </si>
+  <si>
+    <t>PPO_850</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-BASE_9 - at-2026-04-19 08-03-10</t>
+  </si>
+  <si>
+    <t>PPO_916</t>
+  </si>
+  <si>
+    <t>PPO_917</t>
+  </si>
+  <si>
+    <t>X_1</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_916 - at-2026-04-19 21-26-26</t>
+  </si>
+  <si>
+    <t>PPO_918</t>
+  </si>
+  <si>
+    <t>PPO_827_P2</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_918 - at-2026-04-20 07-32-56</t>
+  </si>
+  <si>
+    <t>PPO_919</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_832 - at-2026-04-20 10-51-30</t>
+  </si>
+  <si>
+    <t>PPO_851</t>
+  </si>
+  <si>
+    <t>PPO_852X</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-X_1 - at-2026-04-20 18-59-49</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-X_1 - at-2026-04-20 22-02-09</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q312"/>
+  <dimension ref="A1:Q349"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -4304,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="N57">
-        <v>0.8333333333333334</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O57">
         <v>0.5</v>
@@ -4313,7 +4421,7 @@
         <v>0.5</v>
       </c>
       <c r="Q57">
-        <v>0.4849370117033828</v>
+        <v>0.484937011703383</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -4357,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="N58">
-        <v>0.6666666666666666</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O58">
         <v>0.5</v>
@@ -4366,7 +4474,7 @@
         <v>0.75</v>
       </c>
       <c r="Q58">
-        <v>0.5801106795782706</v>
+        <v>0.580110679578271</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -4410,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="N59">
-        <v>0.6666666666666666</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O59">
         <v>0.5</v>
@@ -4419,7 +4527,7 @@
         <v>1</v>
       </c>
       <c r="Q59">
-        <v>0.6917077938306613</v>
+        <v>0.6917077938306611</v>
       </c>
     </row>
     <row r="60" spans="1:17">
@@ -4457,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>0.3333333333333333</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -4525,7 +4633,7 @@
         <v>0.5</v>
       </c>
       <c r="Q61">
-        <v>0.4384106689177569</v>
+        <v>0.438410668917757</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -4578,7 +4686,7 @@
         <v>0.5</v>
       </c>
       <c r="Q62">
-        <v>0.4241692374208583</v>
+        <v>0.424169237420858</v>
       </c>
     </row>
     <row r="63" spans="1:17">
@@ -4631,7 +4739,7 @@
         <v>0.5</v>
       </c>
       <c r="Q63">
-        <v>0.5895043151708943</v>
+        <v>0.589504315170894</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -4684,7 +4792,7 @@
         <v>0.5</v>
       </c>
       <c r="Q64">
-        <v>0.5382289003609197</v>
+        <v>0.53822890036092</v>
       </c>
     </row>
     <row r="65" spans="1:17">
@@ -4737,7 +4845,7 @@
         <v>0.5</v>
       </c>
       <c r="Q65">
-        <v>0.5911434472243706</v>
+        <v>0.591143447224371</v>
       </c>
     </row>
     <row r="66" spans="1:17">
@@ -4790,7 +4898,7 @@
         <v>0.5</v>
       </c>
       <c r="Q66">
-        <v>0.3891082706231538</v>
+        <v>0.389108270623154</v>
       </c>
     </row>
     <row r="67" spans="1:17">
@@ -4843,7 +4951,7 @@
         <v>0.5</v>
       </c>
       <c r="Q67">
-        <v>0.5950434510757453</v>
+        <v>0.595043451075745</v>
       </c>
     </row>
     <row r="68" spans="1:17">
@@ -4896,7 +5004,7 @@
         <v>0.5</v>
       </c>
       <c r="Q68">
-        <v>0.5703766614991347</v>
+        <v>0.570376661499135</v>
       </c>
     </row>
     <row r="69" spans="1:17">
@@ -5002,7 +5110,7 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>0.2987305034074406</v>
+        <v>0.298730503407441</v>
       </c>
     </row>
     <row r="71" spans="1:17">
@@ -5055,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>0.2469057687801435</v>
+        <v>0.246905768780144</v>
       </c>
     </row>
     <row r="72" spans="1:17">
@@ -5108,7 +5216,7 @@
         <v>0.5</v>
       </c>
       <c r="Q72">
-        <v>0.5305495779947422</v>
+        <v>0.530549577994742</v>
       </c>
     </row>
     <row r="73" spans="1:17">
@@ -5161,7 +5269,7 @@
         <v>0.5</v>
       </c>
       <c r="Q73">
-        <v>0.5117528707367589</v>
+        <v>0.511752870736759</v>
       </c>
     </row>
     <row r="74" spans="1:17">
@@ -5267,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0.05454674256225125</v>
+        <v>0.0545467425622513</v>
       </c>
     </row>
     <row r="76" spans="1:17">
@@ -5320,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>0.04360525349632208</v>
+        <v>0.0436052534963221</v>
       </c>
     </row>
     <row r="77" spans="1:17">
@@ -5373,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="Q77">
-        <v>0.2987305034074406</v>
+        <v>0.298730503407441</v>
       </c>
     </row>
     <row r="78" spans="1:17">
@@ -5426,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>0.2987305034074406</v>
+        <v>0.298730503407441</v>
       </c>
     </row>
     <row r="79" spans="1:17">
@@ -5479,7 +5587,7 @@
         <v>0.5</v>
       </c>
       <c r="Q79">
-        <v>0.2602820668693018</v>
+        <v>0.260282066869302</v>
       </c>
     </row>
     <row r="80" spans="1:17">
@@ -5532,7 +5640,7 @@
         <v>0.5</v>
       </c>
       <c r="Q80">
-        <v>0.5405575983127551</v>
+        <v>0.540557598312755</v>
       </c>
     </row>
     <row r="81" spans="1:17">
@@ -5585,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>0.1771596893854673</v>
+        <v>0.177159689385467</v>
       </c>
     </row>
     <row r="82" spans="1:17">
@@ -5638,7 +5746,7 @@
         <v>0</v>
       </c>
       <c r="Q82">
-        <v>0.02017828079624298</v>
+        <v>0.020178280796243</v>
       </c>
     </row>
     <row r="83" spans="1:17">
@@ -5691,7 +5799,7 @@
         <v>0.5</v>
       </c>
       <c r="Q83">
-        <v>0.4444926390560648</v>
+        <v>0.444492639056065</v>
       </c>
     </row>
     <row r="84" spans="1:17">
@@ -5744,7 +5852,7 @@
         <v>0.5</v>
       </c>
       <c r="Q84">
-        <v>0.6212410509014697</v>
+        <v>0.62124105090147</v>
       </c>
     </row>
     <row r="85" spans="1:17">
@@ -5797,7 +5905,7 @@
         <v>0.5</v>
       </c>
       <c r="Q85">
-        <v>0.4785179015683706</v>
+        <v>0.478517901568371</v>
       </c>
     </row>
     <row r="86" spans="1:17">
@@ -5850,7 +5958,7 @@
         <v>0.5</v>
       </c>
       <c r="Q86">
-        <v>0.6212693117989435</v>
+        <v>0.621269311798944</v>
       </c>
     </row>
     <row r="87" spans="1:17">
@@ -5903,7 +6011,7 @@
         <v>0.5</v>
       </c>
       <c r="Q87">
-        <v>0.5950434510757453</v>
+        <v>0.595043451075745</v>
       </c>
     </row>
     <row r="88" spans="1:17">
@@ -5956,7 +6064,7 @@
         <v>0.5</v>
       </c>
       <c r="Q88">
-        <v>0.5835443329496445</v>
+        <v>0.583544332949645</v>
       </c>
     </row>
     <row r="89" spans="1:17">
@@ -6009,7 +6117,7 @@
         <v>0.5</v>
       </c>
       <c r="Q89">
-        <v>0.3726134741896137</v>
+        <v>0.372613474189614</v>
       </c>
     </row>
     <row r="90" spans="1:17">
@@ -6062,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="Q90">
-        <v>0.2577907360511252</v>
+        <v>0.257790736051125</v>
       </c>
     </row>
     <row r="91" spans="1:17">
@@ -6115,7 +6223,7 @@
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>0.1469556825268395</v>
+        <v>0.14695568252684</v>
       </c>
     </row>
     <row r="92" spans="1:17">
@@ -6168,7 +6276,7 @@
         <v>0.5</v>
       </c>
       <c r="Q92">
-        <v>0.4504233590415303</v>
+        <v>0.45042335904153</v>
       </c>
     </row>
     <row r="93" spans="1:17">
@@ -6327,7 +6435,7 @@
         <v>0.5</v>
       </c>
       <c r="Q95">
-        <v>0.5608244781530141</v>
+        <v>0.5608244781530139</v>
       </c>
     </row>
     <row r="96" spans="1:17">
@@ -6380,7 +6488,7 @@
         <v>0.5</v>
       </c>
       <c r="Q96">
-        <v>0.5950434510757453</v>
+        <v>0.595043451075745</v>
       </c>
     </row>
     <row r="97" spans="1:17">
@@ -6433,7 +6541,7 @@
         <v>0.5</v>
       </c>
       <c r="Q97">
-        <v>0.5224160193539052</v>
+        <v>0.522416019353905</v>
       </c>
     </row>
     <row r="98" spans="1:17">
@@ -6486,7 +6594,7 @@
         <v>0.5</v>
       </c>
       <c r="Q98">
-        <v>0.6212693117989435</v>
+        <v>0.621269311798944</v>
       </c>
     </row>
     <row r="99" spans="1:17">
@@ -6539,7 +6647,7 @@
         <v>0.5</v>
       </c>
       <c r="Q99">
-        <v>0.5621764794881573</v>
+        <v>0.562176479488157</v>
       </c>
     </row>
     <row r="100" spans="1:17">
@@ -6592,7 +6700,7 @@
         <v>0.5</v>
       </c>
       <c r="Q100">
-        <v>0.5497749194151453</v>
+        <v>0.549774919415145</v>
       </c>
     </row>
     <row r="101" spans="1:17">
@@ -6698,7 +6806,7 @@
         <v>0.5</v>
       </c>
       <c r="Q102">
-        <v>0.6074592285958409</v>
+        <v>0.607459228595841</v>
       </c>
     </row>
     <row r="103" spans="1:17">
@@ -6751,7 +6859,7 @@
         <v>0.5</v>
       </c>
       <c r="Q103">
-        <v>0.4392821250704512</v>
+        <v>0.439282125070451</v>
       </c>
     </row>
     <row r="104" spans="1:17">
@@ -6857,7 +6965,7 @@
         <v>0.5</v>
       </c>
       <c r="Q105">
-        <v>0.5702070961142923</v>
+        <v>0.570207096114292</v>
       </c>
     </row>
     <row r="106" spans="1:17">
@@ -6910,7 +7018,7 @@
         <v>0.5</v>
       </c>
       <c r="Q106">
-        <v>0.5702918788067135</v>
+        <v>0.5702918788067139</v>
       </c>
     </row>
     <row r="107" spans="1:17">
@@ -6963,7 +7071,7 @@
         <v>0.5</v>
       </c>
       <c r="Q107">
-        <v>0.5326734138312264</v>
+        <v>0.532673413831226</v>
       </c>
     </row>
     <row r="108" spans="1:17">
@@ -7016,7 +7124,7 @@
         <v>0.5</v>
       </c>
       <c r="Q108">
-        <v>0.5703201397041872</v>
+        <v>0.570320139704187</v>
       </c>
     </row>
     <row r="109" spans="1:17">
@@ -7069,7 +7177,7 @@
         <v>0.5</v>
       </c>
       <c r="Q109">
-        <v>0.5178608872033972</v>
+        <v>0.517860887203397</v>
       </c>
     </row>
     <row r="110" spans="1:17">
@@ -7122,7 +7230,7 @@
         <v>0.5</v>
       </c>
       <c r="Q110">
-        <v>0.5703766614991347</v>
+        <v>0.570376661499135</v>
       </c>
     </row>
     <row r="111" spans="1:17">
@@ -7175,7 +7283,7 @@
         <v>0.5</v>
       </c>
       <c r="Q111">
-        <v>0.4712543976580441</v>
+        <v>0.471254397658044</v>
       </c>
     </row>
     <row r="112" spans="1:17">
@@ -7228,7 +7336,7 @@
         <v>0.5</v>
       </c>
       <c r="Q112">
-        <v>0.5950434510757453</v>
+        <v>0.595043451075745</v>
       </c>
     </row>
     <row r="113" spans="1:17">
@@ -7281,7 +7389,7 @@
         <v>0.5</v>
       </c>
       <c r="Q113">
-        <v>0.5798723230503079</v>
+        <v>0.579872323050308</v>
       </c>
     </row>
     <row r="114" spans="1:17">
@@ -7334,7 +7442,7 @@
         <v>0.5</v>
       </c>
       <c r="Q114">
-        <v>0.5365162899740117</v>
+        <v>0.536516289974012</v>
       </c>
     </row>
     <row r="115" spans="1:17">
@@ -7440,7 +7548,7 @@
         <v>0.5</v>
       </c>
       <c r="Q116">
-        <v>0.7204577471541457</v>
+        <v>0.720457747154146</v>
       </c>
     </row>
     <row r="117" spans="1:17">
@@ -7493,7 +7601,7 @@
         <v>0.5</v>
       </c>
       <c r="Q117">
-        <v>0.5381842888386036</v>
+        <v>0.538184288838604</v>
       </c>
     </row>
     <row r="118" spans="1:17">
@@ -7546,7 +7654,7 @@
         <v>0.5</v>
       </c>
       <c r="Q118">
-        <v>0.5736795238912485</v>
+        <v>0.573679523891249</v>
       </c>
     </row>
     <row r="119" spans="1:17">
@@ -7599,7 +7707,7 @@
         <v>0.5</v>
       </c>
       <c r="Q119">
-        <v>0.4679866883858624</v>
+        <v>0.467986688385862</v>
       </c>
     </row>
     <row r="120" spans="1:17">
@@ -7652,7 +7760,7 @@
         <v>0.5</v>
       </c>
       <c r="Q120">
-        <v>0.5263483999746443</v>
+        <v>0.526348399974644</v>
       </c>
     </row>
     <row r="121" spans="1:17">
@@ -7705,7 +7813,7 @@
         <v>0.5</v>
       </c>
       <c r="Q121">
-        <v>0.5400737004853258</v>
+        <v>0.540073700485326</v>
       </c>
     </row>
     <row r="122" spans="1:17">
@@ -7758,7 +7866,7 @@
         <v>0.5</v>
       </c>
       <c r="Q122">
-        <v>0.7205142689490933</v>
+        <v>0.720514268949093</v>
       </c>
     </row>
     <row r="123" spans="1:17">
@@ -7864,7 +7972,7 @@
         <v>0.5</v>
       </c>
       <c r="Q124">
-        <v>0.4592916996131351</v>
+        <v>0.459291699613135</v>
       </c>
     </row>
     <row r="125" spans="1:17">
@@ -8023,7 +8131,7 @@
         <v>0.5</v>
       </c>
       <c r="Q127">
-        <v>0.4639905974830771</v>
+        <v>0.463990597483077</v>
       </c>
     </row>
     <row r="128" spans="1:17">
@@ -8076,7 +8184,7 @@
         <v>0.5</v>
       </c>
       <c r="Q128">
-        <v>0.5392676986041566</v>
+        <v>0.539267698604157</v>
       </c>
     </row>
     <row r="129" spans="1:17">
@@ -8129,7 +8237,7 @@
         <v>0.5</v>
       </c>
       <c r="Q129">
-        <v>0.7166142650977186</v>
+        <v>0.716614265097719</v>
       </c>
     </row>
     <row r="130" spans="1:17">
@@ -8182,7 +8290,7 @@
         <v>0.5</v>
       </c>
       <c r="Q130">
-        <v>0.7164729606103499</v>
+        <v>0.71647296061035</v>
       </c>
     </row>
     <row r="131" spans="1:17">
@@ -8235,7 +8343,7 @@
         <v>0.5</v>
       </c>
       <c r="Q131">
-        <v>0.5687092685481846</v>
+        <v>0.568709268548185</v>
       </c>
     </row>
     <row r="132" spans="1:17">
@@ -8288,7 +8396,7 @@
         <v>0.5</v>
       </c>
       <c r="Q132">
-        <v>0.4697141377317027</v>
+        <v>0.469714137731703</v>
       </c>
     </row>
     <row r="133" spans="1:17">
@@ -8341,7 +8449,7 @@
         <v>0.5</v>
       </c>
       <c r="Q133">
-        <v>0.5743331871454569</v>
+        <v>0.574333187145457</v>
       </c>
     </row>
     <row r="134" spans="1:17">
@@ -8447,7 +8555,7 @@
         <v>0.5</v>
       </c>
       <c r="Q135">
-        <v>0.6382622955365634</v>
+        <v>0.638262295536563</v>
       </c>
     </row>
     <row r="136" spans="1:17">
@@ -8500,7 +8608,7 @@
         <v>0.5</v>
       </c>
       <c r="Q136">
-        <v>0.7040901657732606</v>
+        <v>0.704090165773261</v>
       </c>
     </row>
     <row r="137" spans="1:17">
@@ -8553,7 +8661,7 @@
         <v>0.5</v>
       </c>
       <c r="Q137">
-        <v>0.7269801814213388</v>
+        <v>0.726980181421339</v>
       </c>
     </row>
     <row r="138" spans="1:17">
@@ -8606,7 +8714,7 @@
         <v>0.5</v>
       </c>
       <c r="Q138">
-        <v>0.3628966993766061</v>
+        <v>0.362896699376606</v>
       </c>
     </row>
     <row r="139" spans="1:17">
@@ -8659,7 +8767,7 @@
         <v>1</v>
       </c>
       <c r="Q139">
-        <v>0.7398267569299187</v>
+        <v>0.7398267569299189</v>
       </c>
     </row>
     <row r="140" spans="1:17">
@@ -8712,7 +8820,7 @@
         <v>0.5</v>
       </c>
       <c r="Q140">
-        <v>0.6952503379132217</v>
+        <v>0.695250337913222</v>
       </c>
     </row>
     <row r="141" spans="1:17">
@@ -8818,7 +8926,7 @@
         <v>0.5</v>
       </c>
       <c r="Q142">
-        <v>0.4577793767406084</v>
+        <v>0.457779376740608</v>
       </c>
     </row>
     <row r="143" spans="1:17">
@@ -8871,7 +8979,7 @@
         <v>0.5</v>
       </c>
       <c r="Q143">
-        <v>0.5758027538140909</v>
+        <v>0.575802753814091</v>
       </c>
     </row>
     <row r="144" spans="1:17">
@@ -8924,7 +9032,7 @@
         <v>1</v>
       </c>
       <c r="Q144">
-        <v>0.7848577613994315</v>
+        <v>0.784857761399432</v>
       </c>
     </row>
     <row r="145" spans="1:17">
@@ -9030,7 +9138,7 @@
         <v>0.5</v>
       </c>
       <c r="Q146">
-        <v>0.5390455992838874</v>
+        <v>0.539045599283887</v>
       </c>
     </row>
     <row r="147" spans="1:17">
@@ -9083,7 +9191,7 @@
         <v>0.5</v>
       </c>
       <c r="Q147">
-        <v>0.4292790786703937</v>
+        <v>0.429279078670394</v>
       </c>
     </row>
     <row r="148" spans="1:17">
@@ -9136,7 +9244,7 @@
         <v>0.5</v>
       </c>
       <c r="Q148">
-        <v>0.7165294824052973</v>
+        <v>0.716529482405297</v>
       </c>
     </row>
     <row r="149" spans="1:17">
@@ -9189,7 +9297,7 @@
         <v>0.5</v>
       </c>
       <c r="Q149">
-        <v>0.4703746932083696</v>
+        <v>0.47037469320837</v>
       </c>
     </row>
     <row r="150" spans="1:17">
@@ -9242,7 +9350,7 @@
         <v>0.5</v>
       </c>
       <c r="Q150">
-        <v>0.7165294824052973</v>
+        <v>0.716529482405297</v>
       </c>
     </row>
     <row r="151" spans="1:17">
@@ -9348,7 +9456,7 @@
         <v>0.5</v>
       </c>
       <c r="Q152">
-        <v>0.7269519205238651</v>
+        <v>0.726951920523865</v>
       </c>
     </row>
     <row r="153" spans="1:17">
@@ -9401,7 +9509,7 @@
         <v>0.5</v>
       </c>
       <c r="Q153">
-        <v>0.3652862599972408</v>
+        <v>0.365286259997241</v>
       </c>
     </row>
     <row r="154" spans="1:17">
@@ -9454,7 +9562,7 @@
         <v>0.5</v>
       </c>
       <c r="Q154">
-        <v>0.6021416581271839</v>
+        <v>0.602141658127184</v>
       </c>
     </row>
     <row r="155" spans="1:17">
@@ -9613,7 +9721,7 @@
         <v>0.5</v>
       </c>
       <c r="Q157">
-        <v>0.7214410455164877</v>
+        <v>0.721441045516488</v>
       </c>
     </row>
     <row r="158" spans="1:17">
@@ -9666,7 +9774,7 @@
         <v>0.5</v>
       </c>
       <c r="Q158">
-        <v>0.5612443231311023</v>
+        <v>0.561244323131102</v>
       </c>
     </row>
     <row r="159" spans="1:17">
@@ -9719,7 +9827,7 @@
         <v>0.5</v>
       </c>
       <c r="Q159">
-        <v>0.7356853969745306</v>
+        <v>0.7356853969745309</v>
       </c>
     </row>
     <row r="160" spans="1:17">
@@ -9772,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="Q160">
-        <v>0.2816809978748732</v>
+        <v>0.281680997874873</v>
       </c>
     </row>
     <row r="161" spans="1:17">
@@ -9825,7 +9933,7 @@
         <v>0.5</v>
       </c>
       <c r="Q161">
-        <v>0.7214693064139615</v>
+        <v>0.721469306413962</v>
       </c>
     </row>
     <row r="162" spans="1:17">
@@ -9878,7 +9986,7 @@
         <v>0.5</v>
       </c>
       <c r="Q162">
-        <v>0.6742711025868809</v>
+        <v>0.6742711025868811</v>
       </c>
     </row>
     <row r="163" spans="1:17">
@@ -9931,7 +10039,7 @@
         <v>0.5</v>
       </c>
       <c r="Q163">
-        <v>0.7013488587183087</v>
+        <v>0.701348858718309</v>
       </c>
     </row>
     <row r="164" spans="1:17">
@@ -9984,7 +10092,7 @@
         <v>0.5</v>
       </c>
       <c r="Q164">
-        <v>0.4321004940201071</v>
+        <v>0.432100494020107</v>
       </c>
     </row>
     <row r="165" spans="1:17">
@@ -10037,7 +10145,7 @@
         <v>0.5</v>
       </c>
       <c r="Q165">
-        <v>0.7269801814213388</v>
+        <v>0.726980181421339</v>
       </c>
     </row>
     <row r="166" spans="1:17">
@@ -10143,7 +10251,7 @@
         <v>0.5</v>
       </c>
       <c r="Q167">
-        <v>0.7119743502547892</v>
+        <v>0.7119743502547889</v>
       </c>
     </row>
     <row r="168" spans="1:17">
@@ -10196,7 +10304,7 @@
         <v>0.5</v>
       </c>
       <c r="Q168">
-        <v>0.7118895675623681</v>
+        <v>0.711889567562368</v>
       </c>
     </row>
     <row r="169" spans="1:17">
@@ -10302,7 +10410,7 @@
         <v>0.5</v>
       </c>
       <c r="Q170">
-        <v>0.3692993074385104</v>
+        <v>0.36929930743851</v>
       </c>
     </row>
     <row r="171" spans="1:17">
@@ -10408,7 +10516,7 @@
         <v>0.5</v>
       </c>
       <c r="Q172">
-        <v>0.5121804468111775</v>
+        <v>0.512180446811178</v>
       </c>
     </row>
     <row r="173" spans="1:17">
@@ -10461,7 +10569,7 @@
         <v>0.5</v>
       </c>
       <c r="Q173">
-        <v>0.7119460893573155</v>
+        <v>0.711946089357316</v>
       </c>
     </row>
     <row r="174" spans="1:17">
@@ -10514,7 +10622,7 @@
         <v>1</v>
       </c>
       <c r="Q174">
-        <v>0.7283052005085464</v>
+        <v>0.728305200508546</v>
       </c>
     </row>
     <row r="175" spans="1:17">
@@ -10620,7 +10728,7 @@
         <v>1</v>
       </c>
       <c r="Q176">
-        <v>0.7486003412462792</v>
+        <v>0.7486003412462791</v>
       </c>
     </row>
     <row r="177" spans="1:17">
@@ -10673,7 +10781,7 @@
         <v>0.5</v>
       </c>
       <c r="Q177">
-        <v>0.3850795866741993</v>
+        <v>0.385079586674199</v>
       </c>
     </row>
     <row r="178" spans="1:17">
@@ -10726,7 +10834,7 @@
         <v>0.5</v>
       </c>
       <c r="Q178">
-        <v>0.4735899965574943</v>
+        <v>0.473589996557494</v>
       </c>
     </row>
     <row r="179" spans="1:17">
@@ -10779,7 +10887,7 @@
         <v>0.5</v>
       </c>
       <c r="Q179">
-        <v>0.7228310566282973</v>
+        <v>0.7228310566282971</v>
       </c>
     </row>
     <row r="180" spans="1:17">
@@ -10885,7 +10993,7 @@
         <v>0.5</v>
       </c>
       <c r="Q181">
-        <v>0.6262897305985714</v>
+        <v>0.626289730598571</v>
       </c>
     </row>
     <row r="182" spans="1:17">
@@ -10938,7 +11046,7 @@
         <v>0.5</v>
       </c>
       <c r="Q182">
-        <v>0.7322977518899958</v>
+        <v>0.732297751889996</v>
       </c>
     </row>
     <row r="183" spans="1:17">
@@ -10991,7 +11099,7 @@
         <v>0.5</v>
       </c>
       <c r="Q183">
-        <v>0.3944049774485291</v>
+        <v>0.394404977448529</v>
       </c>
     </row>
     <row r="184" spans="1:17">
@@ -11044,7 +11152,7 @@
         <v>1</v>
       </c>
       <c r="Q184">
-        <v>0.7485155585538579</v>
+        <v>0.748515558553858</v>
       </c>
     </row>
     <row r="185" spans="1:17">
@@ -11097,7 +11205,7 @@
         <v>0.5</v>
       </c>
       <c r="Q185">
-        <v>0.5188159246682654</v>
+        <v>0.518815924668265</v>
       </c>
     </row>
     <row r="186" spans="1:17">
@@ -11150,7 +11258,7 @@
         <v>0</v>
       </c>
       <c r="Q186">
-        <v>0.08666694819499343</v>
+        <v>0.0866669481949934</v>
       </c>
     </row>
     <row r="187" spans="1:17">
@@ -11203,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="Q187">
-        <v>0.1632288314961394</v>
+        <v>0.163228831496139</v>
       </c>
     </row>
     <row r="188" spans="1:17">
@@ -11256,7 +11364,7 @@
         <v>0.5</v>
       </c>
       <c r="Q188">
-        <v>0.5729791781561571</v>
+        <v>0.572979178156157</v>
       </c>
     </row>
     <row r="189" spans="1:17">
@@ -11362,7 +11470,7 @@
         <v>0.5</v>
       </c>
       <c r="Q190">
-        <v>0.4750882299953071</v>
+        <v>0.475088229995307</v>
       </c>
     </row>
     <row r="191" spans="1:17">
@@ -11415,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="Q191">
-        <v>0.2214846879821252</v>
+        <v>0.221484687982125</v>
       </c>
     </row>
     <row r="192" spans="1:17">
@@ -11468,7 +11576,7 @@
         <v>0</v>
       </c>
       <c r="Q192">
-        <v>0.2214846879821252</v>
+        <v>0.221484687982125</v>
       </c>
     </row>
     <row r="193" spans="1:17">
@@ -11521,7 +11629,7 @@
         <v>0</v>
       </c>
       <c r="Q193">
-        <v>0.2753735360233808</v>
+        <v>0.275373536023381</v>
       </c>
     </row>
     <row r="194" spans="1:17">
@@ -11574,7 +11682,7 @@
         <v>0.5</v>
       </c>
       <c r="Q194">
-        <v>0.5922456222258461</v>
+        <v>0.592245622225846</v>
       </c>
     </row>
     <row r="195" spans="1:17">
@@ -11680,7 +11788,7 @@
         <v>1</v>
       </c>
       <c r="Q196">
-        <v>0.7435893721238788</v>
+        <v>0.743589372123879</v>
       </c>
     </row>
     <row r="197" spans="1:17">
@@ -11733,7 +11841,7 @@
         <v>0.5</v>
       </c>
       <c r="Q197">
-        <v>0.3944614992434765</v>
+        <v>0.394461499243477</v>
       </c>
     </row>
     <row r="198" spans="1:17">
@@ -11786,7 +11894,7 @@
         <v>1</v>
       </c>
       <c r="Q198">
-        <v>0.7794316690844754</v>
+        <v>0.779431669084475</v>
       </c>
     </row>
     <row r="199" spans="1:17">
@@ -11998,7 +12106,7 @@
         <v>0.5</v>
       </c>
       <c r="Q202">
-        <v>0.5585649176607586</v>
+        <v>0.558564917660759</v>
       </c>
     </row>
     <row r="203" spans="1:17">
@@ -12104,7 +12212,7 @@
         <v>1</v>
       </c>
       <c r="Q204">
-        <v>0.7849708049893264</v>
+        <v>0.784970804989326</v>
       </c>
     </row>
     <row r="205" spans="1:17">
@@ -12157,7 +12265,7 @@
         <v>0.5</v>
       </c>
       <c r="Q205">
-        <v>0.3157481251220145</v>
+        <v>0.315748125122015</v>
       </c>
     </row>
     <row r="206" spans="1:17">
@@ -12210,7 +12318,7 @@
         <v>0.5</v>
       </c>
       <c r="Q206">
-        <v>0.5585931785582322</v>
+        <v>0.558593178558232</v>
       </c>
     </row>
     <row r="207" spans="1:17">
@@ -12263,7 +12371,7 @@
         <v>0.5</v>
       </c>
       <c r="Q207">
-        <v>0.5738208283786171</v>
+        <v>0.573820828378617</v>
       </c>
     </row>
     <row r="208" spans="1:17">
@@ -12316,7 +12424,7 @@
         <v>0.5</v>
       </c>
       <c r="Q208">
-        <v>0.4445349893882524</v>
+        <v>0.444534989388252</v>
       </c>
     </row>
     <row r="209" spans="1:17">
@@ -12369,7 +12477,7 @@
         <v>0.5</v>
       </c>
       <c r="Q209">
-        <v>0.5737925674811434</v>
+        <v>0.573792567481143</v>
       </c>
     </row>
     <row r="210" spans="1:17">
@@ -12422,7 +12530,7 @@
         <v>0.5</v>
       </c>
       <c r="Q210">
-        <v>0.6173410470500951</v>
+        <v>0.617341047050095</v>
       </c>
     </row>
     <row r="211" spans="1:17">
@@ -12475,7 +12583,7 @@
         <v>0.5</v>
       </c>
       <c r="Q211">
-        <v>0.4991580061250267</v>
+        <v>0.499158006125027</v>
       </c>
     </row>
     <row r="212" spans="1:17">
@@ -12528,7 +12636,7 @@
         <v>0.5</v>
       </c>
       <c r="Q212">
-        <v>0.5698077809373475</v>
+        <v>0.569807780937348</v>
       </c>
     </row>
     <row r="213" spans="1:17">
@@ -12581,7 +12689,7 @@
         <v>0.5</v>
       </c>
       <c r="Q213">
-        <v>0.5589793354613133</v>
+        <v>0.558979335461313</v>
       </c>
     </row>
     <row r="214" spans="1:17">
@@ -12634,7 +12742,7 @@
         <v>0.5</v>
       </c>
       <c r="Q214">
-        <v>0.6168701074545929</v>
+        <v>0.616870107454593</v>
       </c>
     </row>
     <row r="215" spans="1:17">
@@ -12687,7 +12795,7 @@
         <v>0.5</v>
       </c>
       <c r="Q215">
-        <v>0.5025105440739531</v>
+        <v>0.502510544073953</v>
       </c>
     </row>
     <row r="216" spans="1:17">
@@ -12740,7 +12848,7 @@
         <v>0</v>
       </c>
       <c r="Q216">
-        <v>0.3190828713321217</v>
+        <v>0.319082871332122</v>
       </c>
     </row>
     <row r="217" spans="1:17">
@@ -12793,7 +12901,7 @@
         <v>0.5</v>
       </c>
       <c r="Q217">
-        <v>0.7426986212916115</v>
+        <v>0.742698621291612</v>
       </c>
     </row>
     <row r="218" spans="1:17">
@@ -12846,7 +12954,7 @@
         <v>1</v>
       </c>
       <c r="Q218">
-        <v>0.9669812786973371</v>
+        <v>0.966981278697337</v>
       </c>
     </row>
     <row r="219" spans="1:17">
@@ -12899,7 +13007,7 @@
         <v>1</v>
       </c>
       <c r="Q219">
-        <v>0.9051314940987577</v>
+        <v>0.905131494098758</v>
       </c>
     </row>
     <row r="220" spans="1:17">
@@ -12952,7 +13060,7 @@
         <v>1</v>
       </c>
       <c r="Q220">
-        <v>0.9367031861880865</v>
+        <v>0.936703186188087</v>
       </c>
     </row>
     <row r="221" spans="1:17">
@@ -13005,7 +13113,7 @@
         <v>1</v>
       </c>
       <c r="Q221">
-        <v>0.9579540697826885</v>
+        <v>0.957954069782689</v>
       </c>
     </row>
     <row r="222" spans="1:17">
@@ -13111,7 +13219,7 @@
         <v>1</v>
       </c>
       <c r="Q223">
-        <v>0.8827570295684978</v>
+        <v>0.882757029568498</v>
       </c>
     </row>
     <row r="224" spans="1:17">
@@ -13164,7 +13272,7 @@
         <v>1</v>
       </c>
       <c r="Q224">
-        <v>0.9709378043436592</v>
+        <v>0.970937804343659</v>
       </c>
     </row>
     <row r="225" spans="1:17">
@@ -13217,7 +13325,7 @@
         <v>1</v>
       </c>
       <c r="Q225">
-        <v>0.9731817196030733</v>
+        <v>0.973181719603073</v>
       </c>
     </row>
     <row r="226" spans="1:17">
@@ -13323,7 +13431,7 @@
         <v>1</v>
       </c>
       <c r="Q227">
-        <v>0.8120836682563628</v>
+        <v>0.812083668256363</v>
       </c>
     </row>
     <row r="228" spans="1:17">
@@ -13376,7 +13484,7 @@
         <v>1</v>
       </c>
       <c r="Q228">
-        <v>0.8918093070296413</v>
+        <v>0.891809307029641</v>
       </c>
     </row>
     <row r="229" spans="1:17">
@@ -13429,7 +13537,7 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>0.2113545172826155</v>
+        <v>0.211354517282616</v>
       </c>
     </row>
     <row r="230" spans="1:17">
@@ -13482,7 +13590,7 @@
         <v>0.5</v>
       </c>
       <c r="Q230">
-        <v>0.4990115739804204</v>
+        <v>0.49901157398042</v>
       </c>
     </row>
     <row r="231" spans="1:17">
@@ -13535,7 +13643,7 @@
         <v>1</v>
       </c>
       <c r="Q231">
-        <v>0.9709378043436592</v>
+        <v>0.970937804343659</v>
       </c>
     </row>
     <row r="232" spans="1:17">
@@ -13588,7 +13696,7 @@
         <v>0.5</v>
       </c>
       <c r="Q232">
-        <v>0.5840217010609907</v>
+        <v>0.584021701060991</v>
       </c>
     </row>
     <row r="233" spans="1:17">
@@ -13641,7 +13749,7 @@
         <v>0.5</v>
       </c>
       <c r="Q233">
-        <v>0.5653091705817869</v>
+        <v>0.565309170581787</v>
       </c>
     </row>
     <row r="234" spans="1:17">
@@ -13747,7 +13855,7 @@
         <v>0.5</v>
       </c>
       <c r="Q235">
-        <v>0.5500815207614019</v>
+        <v>0.550081520761402</v>
       </c>
     </row>
     <row r="236" spans="1:17">
@@ -13853,7 +13961,7 @@
         <v>0.5</v>
       </c>
       <c r="Q237">
-        <v>0.6943449300208425</v>
+        <v>0.694344930020843</v>
       </c>
     </row>
     <row r="238" spans="1:17">
@@ -13906,7 +14014,7 @@
         <v>0.5</v>
       </c>
       <c r="Q238">
-        <v>0.6730092637338194</v>
+        <v>0.673009263733819</v>
       </c>
     </row>
     <row r="239" spans="1:17">
@@ -13959,7 +14067,7 @@
         <v>1</v>
       </c>
       <c r="Q239">
-        <v>0.9709095434461854</v>
+        <v>0.970909543446185</v>
       </c>
     </row>
     <row r="240" spans="1:17">
@@ -14012,7 +14120,7 @@
         <v>0</v>
       </c>
       <c r="Q240">
-        <v>0.4032451287598118</v>
+        <v>0.403245128759812</v>
       </c>
     </row>
     <row r="241" spans="1:17">
@@ -14065,7 +14173,7 @@
         <v>0.5</v>
       </c>
       <c r="Q241">
-        <v>0.7095160580462799</v>
+        <v>0.70951605804628</v>
       </c>
     </row>
     <row r="242" spans="1:17">
@@ -14118,7 +14226,7 @@
         <v>0.5</v>
       </c>
       <c r="Q242">
-        <v>0.7172991092105451</v>
+        <v>0.717299109210545</v>
       </c>
     </row>
     <row r="243" spans="1:17">
@@ -14171,7 +14279,7 @@
         <v>0.5</v>
       </c>
       <c r="Q243">
-        <v>0.6164284419454606</v>
+        <v>0.616428441945461</v>
       </c>
     </row>
     <row r="244" spans="1:17">
@@ -14224,7 +14332,7 @@
         <v>0.5</v>
       </c>
       <c r="Q244">
-        <v>0.7055595323999577</v>
+        <v>0.7055595323999579</v>
       </c>
     </row>
     <row r="245" spans="1:17">
@@ -14277,7 +14385,7 @@
         <v>0.5</v>
       </c>
       <c r="Q245">
-        <v>0.7055877932974316</v>
+        <v>0.705587793297432</v>
       </c>
     </row>
     <row r="246" spans="1:17">
@@ -14330,7 +14438,7 @@
         <v>0.5</v>
       </c>
       <c r="Q246">
-        <v>0.6888057941159915</v>
+        <v>0.688805794115992</v>
       </c>
     </row>
     <row r="247" spans="1:17">
@@ -14383,7 +14491,7 @@
         <v>1</v>
       </c>
       <c r="Q247">
-        <v>0.9731534587055997</v>
+        <v>0.9731534587056</v>
       </c>
     </row>
     <row r="248" spans="1:17">
@@ -14489,7 +14597,7 @@
         <v>1</v>
       </c>
       <c r="Q249">
-        <v>0.9579540697826885</v>
+        <v>0.957954069782689</v>
       </c>
     </row>
     <row r="250" spans="1:17">
@@ -14542,7 +14650,7 @@
         <v>0.5</v>
       </c>
       <c r="Q250">
-        <v>0.6345415067891953</v>
+        <v>0.634541506789195</v>
       </c>
     </row>
     <row r="251" spans="1:17">
@@ -14595,7 +14703,7 @@
         <v>0.5</v>
       </c>
       <c r="Q251">
-        <v>0.6902753607846255</v>
+        <v>0.690275360784626</v>
       </c>
     </row>
     <row r="252" spans="1:17">
@@ -14648,7 +14756,7 @@
         <v>0</v>
       </c>
       <c r="Q252">
-        <v>0.4296913770954323</v>
+        <v>0.429691377095432</v>
       </c>
     </row>
     <row r="253" spans="1:17">
@@ -14701,7 +14809,7 @@
         <v>1</v>
       </c>
       <c r="Q253">
-        <v>0.9440912630492588</v>
+        <v>0.9440912630492591</v>
       </c>
     </row>
     <row r="254" spans="1:17">
@@ -14860,7 +14968,7 @@
         <v>1</v>
       </c>
       <c r="Q256">
-        <v>0.9579258088852146</v>
+        <v>0.9579258088852149</v>
       </c>
     </row>
     <row r="257" spans="1:17">
@@ -14913,7 +15021,7 @@
         <v>0.5</v>
       </c>
       <c r="Q257">
-        <v>0.6903318825795729</v>
+        <v>0.690331882579573</v>
       </c>
     </row>
     <row r="258" spans="1:17">
@@ -14966,7 +15074,7 @@
         <v>0.5</v>
       </c>
       <c r="Q258">
-        <v>0.6965323234853092</v>
+        <v>0.696532323485309</v>
       </c>
     </row>
     <row r="259" spans="1:17">
@@ -15019,7 +15127,7 @@
         <v>0.5</v>
       </c>
       <c r="Q259">
-        <v>0.7055595323999577</v>
+        <v>0.7055595323999579</v>
       </c>
     </row>
     <row r="260" spans="1:17">
@@ -15072,7 +15180,7 @@
         <v>0.5</v>
       </c>
       <c r="Q260">
-        <v>0.7095443189437537</v>
+        <v>0.709544318943754</v>
       </c>
     </row>
     <row r="261" spans="1:17">
@@ -15125,7 +15233,7 @@
         <v>0.5</v>
       </c>
       <c r="Q261">
-        <v>0.7095443189437537</v>
+        <v>0.709544318943754</v>
       </c>
     </row>
     <row r="262" spans="1:17">
@@ -15178,7 +15286,7 @@
         <v>1</v>
       </c>
       <c r="Q262">
-        <v>0.9731534587055997</v>
+        <v>0.9731534587056</v>
       </c>
     </row>
     <row r="263" spans="1:17">
@@ -15231,7 +15339,7 @@
         <v>1</v>
       </c>
       <c r="Q263">
-        <v>0.8334475954408596</v>
+        <v>0.83344759544086</v>
       </c>
     </row>
     <row r="264" spans="1:17">
@@ -15284,7 +15392,7 @@
         <v>0.5</v>
       </c>
       <c r="Q264">
-        <v>0.6068903480340537</v>
+        <v>0.606890348034054</v>
       </c>
     </row>
     <row r="265" spans="1:17">
@@ -15337,7 +15445,7 @@
         <v>1</v>
       </c>
       <c r="Q265">
-        <v>0.9669812786973371</v>
+        <v>0.966981278697337</v>
       </c>
     </row>
     <row r="266" spans="1:17">
@@ -15390,7 +15498,7 @@
         <v>1</v>
       </c>
       <c r="Q266">
-        <v>0.9085913062110814</v>
+        <v>0.908591306211081</v>
       </c>
     </row>
     <row r="267" spans="1:17">
@@ -15443,7 +15551,7 @@
         <v>0.5</v>
       </c>
       <c r="Q267">
-        <v>0.7039769221414289</v>
+        <v>0.703976922141429</v>
       </c>
     </row>
     <row r="268" spans="1:17">
@@ -15496,7 +15604,7 @@
         <v>0.5</v>
       </c>
       <c r="Q268">
-        <v>0.7011790932915297</v>
+        <v>0.7011790932915301</v>
       </c>
     </row>
     <row r="269" spans="1:17">
@@ -15549,7 +15657,7 @@
         <v>0.5</v>
       </c>
       <c r="Q269">
-        <v>0.7039769221414289</v>
+        <v>0.703976922141429</v>
       </c>
     </row>
     <row r="270" spans="1:17">
@@ -15602,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="Q270">
-        <v>0.3118066624075094</v>
+        <v>0.311806662407509</v>
       </c>
     </row>
     <row r="271" spans="1:17">
@@ -15655,7 +15763,7 @@
         <v>0</v>
       </c>
       <c r="Q271">
-        <v>0.3937001339007902</v>
+        <v>0.39370013390079</v>
       </c>
     </row>
     <row r="272" spans="1:17">
@@ -15708,7 +15816,7 @@
         <v>1</v>
       </c>
       <c r="Q272">
-        <v>0.9517253679794784</v>
+        <v>0.951725367979478</v>
       </c>
     </row>
     <row r="273" spans="1:17">
@@ -15761,7 +15869,7 @@
         <v>1</v>
       </c>
       <c r="Q273">
-        <v>0.9518101506718996</v>
+        <v>0.9518101506719</v>
       </c>
     </row>
     <row r="274" spans="1:17">
@@ -15867,7 +15975,7 @@
         <v>1</v>
       </c>
       <c r="Q275">
-        <v>0.9770458208102973</v>
+        <v>0.977045820810297</v>
       </c>
     </row>
     <row r="276" spans="1:17">
@@ -15920,7 +16028,7 @@
         <v>1</v>
       </c>
       <c r="Q276">
-        <v>0.8559104882740974</v>
+        <v>0.855910488274097</v>
       </c>
     </row>
     <row r="277" spans="1:17">
@@ -15973,7 +16081,7 @@
         <v>0.5</v>
       </c>
       <c r="Q277">
-        <v>0.6027834023836045</v>
+        <v>0.6027834023836049</v>
       </c>
     </row>
     <row r="278" spans="1:17">
@@ -16026,7 +16134,7 @@
         <v>0.5</v>
       </c>
       <c r="Q278">
-        <v>0.6651864223111297</v>
+        <v>0.66518642231113</v>
       </c>
     </row>
     <row r="279" spans="1:17">
@@ -16132,7 +16240,7 @@
         <v>0.5</v>
       </c>
       <c r="Q280">
-        <v>0.5811125931864174</v>
+        <v>0.5811125931864169</v>
       </c>
     </row>
     <row r="281" spans="1:17">
@@ -16185,7 +16293,7 @@
         <v>0.5</v>
       </c>
       <c r="Q281">
-        <v>0.5331167979212558</v>
+        <v>0.533116797921256</v>
       </c>
     </row>
     <row r="282" spans="1:17">
@@ -16238,7 +16346,7 @@
         <v>0.5</v>
       </c>
       <c r="Q282">
-        <v>0.4833725992321002</v>
+        <v>0.4833725992321</v>
       </c>
     </row>
     <row r="283" spans="1:17">
@@ -16291,7 +16399,7 @@
         <v>0</v>
       </c>
       <c r="Q283">
-        <v>0.2985180538063357</v>
+        <v>0.298518053806336</v>
       </c>
     </row>
     <row r="284" spans="1:17">
@@ -16397,7 +16505,7 @@
         <v>0.5</v>
       </c>
       <c r="Q285">
-        <v>0.4610582467612029</v>
+        <v>0.461058246761203</v>
       </c>
     </row>
     <row r="286" spans="1:17">
@@ -16450,7 +16558,7 @@
         <v>1</v>
       </c>
       <c r="Q286">
-        <v>0.9518101506718996</v>
+        <v>0.9518101506719</v>
       </c>
     </row>
     <row r="287" spans="1:17">
@@ -16556,7 +16664,7 @@
         <v>0</v>
       </c>
       <c r="Q288">
-        <v>0.2700693415089417</v>
+        <v>0.270069341508942</v>
       </c>
     </row>
     <row r="289" spans="1:17">
@@ -16609,7 +16717,7 @@
         <v>0.5</v>
       </c>
       <c r="Q289">
-        <v>0.6016152099256304</v>
+        <v>0.60161520992563</v>
       </c>
     </row>
     <row r="290" spans="1:17">
@@ -16662,7 +16770,7 @@
         <v>1</v>
       </c>
       <c r="Q290">
-        <v>0.9709095434461854</v>
+        <v>0.970909543446185</v>
       </c>
     </row>
     <row r="291" spans="1:17">
@@ -16715,7 +16823,7 @@
         <v>0.5</v>
       </c>
       <c r="Q291">
-        <v>0.4856117927059819</v>
+        <v>0.485611792705982</v>
       </c>
     </row>
     <row r="292" spans="1:17">
@@ -16768,7 +16876,7 @@
         <v>1</v>
       </c>
       <c r="Q292">
-        <v>0.9709378043436592</v>
+        <v>0.970937804343659</v>
       </c>
     </row>
     <row r="293" spans="1:17">
@@ -16821,7 +16929,7 @@
         <v>1</v>
       </c>
       <c r="Q293">
-        <v>0.9600810979701512</v>
+        <v>0.960081097970151</v>
       </c>
     </row>
     <row r="294" spans="1:17">
@@ -16874,7 +16982,7 @@
         <v>1</v>
       </c>
       <c r="Q294">
-        <v>0.9709660652411329</v>
+        <v>0.970966065241133</v>
       </c>
     </row>
     <row r="295" spans="1:17">
@@ -16927,7 +17035,7 @@
         <v>1</v>
       </c>
       <c r="Q295">
-        <v>0.9709378043436592</v>
+        <v>0.970937804343659</v>
       </c>
     </row>
     <row r="296" spans="1:17">
@@ -16980,7 +17088,7 @@
         <v>0.5</v>
       </c>
       <c r="Q296">
-        <v>0.4928752966163085</v>
+        <v>0.492875296616309</v>
       </c>
     </row>
     <row r="297" spans="1:17">
@@ -17033,7 +17141,7 @@
         <v>1</v>
       </c>
       <c r="Q297">
-        <v>0.9709378043436592</v>
+        <v>0.970937804343659</v>
       </c>
     </row>
     <row r="298" spans="1:17">
@@ -17086,7 +17194,7 @@
         <v>1</v>
       </c>
       <c r="Q298">
-        <v>0.9259193522343683</v>
+        <v>0.9259193522343681</v>
       </c>
     </row>
     <row r="299" spans="1:17">
@@ -17139,7 +17247,7 @@
         <v>1</v>
       </c>
       <c r="Q299">
-        <v>0.9708812825487118</v>
+        <v>0.970881282548712</v>
       </c>
     </row>
     <row r="300" spans="1:17">
@@ -17192,7 +17300,7 @@
         <v>1</v>
       </c>
       <c r="Q300">
-        <v>0.9709378043436592</v>
+        <v>0.970937804343659</v>
       </c>
     </row>
     <row r="301" spans="1:17">
@@ -17245,7 +17353,7 @@
         <v>1</v>
       </c>
       <c r="Q301">
-        <v>0.9259193522343683</v>
+        <v>0.9259193522343681</v>
       </c>
     </row>
     <row r="302" spans="1:17">
@@ -17298,7 +17406,7 @@
         <v>0.5</v>
       </c>
       <c r="Q302">
-        <v>0.3945343629381099</v>
+        <v>0.39453436293811</v>
       </c>
     </row>
     <row r="303" spans="1:17">
@@ -17351,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="Q303">
-        <v>0.4885403789045588</v>
+        <v>0.488540378904559</v>
       </c>
     </row>
     <row r="304" spans="1:17">
@@ -17457,7 +17565,7 @@
         <v>1</v>
       </c>
       <c r="Q305">
-        <v>0.9344592709286724</v>
+        <v>0.934459270928672</v>
       </c>
     </row>
     <row r="306" spans="1:17">
@@ -17510,7 +17618,7 @@
         <v>0.5</v>
       </c>
       <c r="Q306">
-        <v>0.4451484727471992</v>
+        <v>0.445148472747199</v>
       </c>
     </row>
     <row r="307" spans="1:17">
@@ -17563,7 +17671,7 @@
         <v>1</v>
       </c>
       <c r="Q307">
-        <v>0.9709378043436592</v>
+        <v>0.970937804343659</v>
       </c>
     </row>
     <row r="308" spans="1:17">
@@ -17616,7 +17724,7 @@
         <v>1</v>
       </c>
       <c r="Q308">
-        <v>0.9709660652411329</v>
+        <v>0.970966065241133</v>
       </c>
     </row>
     <row r="309" spans="1:17">
@@ -17669,7 +17777,7 @@
         <v>1</v>
       </c>
       <c r="Q309">
-        <v>0.8620467656382093</v>
+        <v>0.862046765638209</v>
       </c>
     </row>
     <row r="310" spans="1:17">
@@ -17722,7 +17830,7 @@
         <v>0.5</v>
       </c>
       <c r="Q310">
-        <v>0.7466551469379337</v>
+        <v>0.746655146937934</v>
       </c>
     </row>
     <row r="311" spans="1:17">
@@ -17775,7 +17883,7 @@
         <v>0.5</v>
       </c>
       <c r="Q311">
-        <v>0.6718741534372107</v>
+        <v>0.671874153437211</v>
       </c>
     </row>
     <row r="312" spans="1:17">
@@ -17828,7 +17936,1968 @@
         <v>1</v>
       </c>
       <c r="Q312">
+        <v>0.970966065241133</v>
+      </c>
+    </row>
+    <row r="313" spans="1:17">
+      <c r="A313" t="s">
+        <v>307</v>
+      </c>
+      <c r="B313">
+        <v>0.026484</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>0.98</v>
+      </c>
+      <c r="E313">
+        <v>1</v>
+      </c>
+      <c r="F313">
+        <v>1</v>
+      </c>
+      <c r="G313">
+        <v>1</v>
+      </c>
+      <c r="H313">
+        <v>1</v>
+      </c>
+      <c r="I313">
+        <v>0.5</v>
+      </c>
+      <c r="J313">
+        <v>1</v>
+      </c>
+      <c r="K313">
+        <v>1</v>
+      </c>
+      <c r="L313">
+        <v>0.5</v>
+      </c>
+      <c r="M313">
+        <v>1</v>
+      </c>
+      <c r="N313">
+        <v>1</v>
+      </c>
+      <c r="O313">
+        <v>1</v>
+      </c>
+      <c r="P313">
+        <v>1</v>
+      </c>
+      <c r="Q313">
+        <v>0.970853021651238</v>
+      </c>
+    </row>
+    <row r="314" spans="1:17">
+      <c r="A314" t="s">
+        <v>308</v>
+      </c>
+      <c r="B314">
+        <v>0.021875</v>
+      </c>
+      <c r="C314">
+        <v>2000</v>
+      </c>
+      <c r="D314">
+        <v>0.99</v>
+      </c>
+      <c r="E314">
+        <v>1</v>
+      </c>
+      <c r="F314">
+        <v>1</v>
+      </c>
+      <c r="G314">
+        <v>1</v>
+      </c>
+      <c r="H314">
+        <v>1</v>
+      </c>
+      <c r="I314">
+        <v>0.5</v>
+      </c>
+      <c r="J314">
+        <v>1</v>
+      </c>
+      <c r="K314">
+        <v>0.5</v>
+      </c>
+      <c r="L314">
+        <v>0.5</v>
+      </c>
+      <c r="M314">
+        <v>1</v>
+      </c>
+      <c r="N314">
+        <v>0.5</v>
+      </c>
+      <c r="O314">
+        <v>1</v>
+      </c>
+      <c r="P314">
+        <v>0.5</v>
+      </c>
+      <c r="Q314">
+        <v>0.673009263733819</v>
+      </c>
+    </row>
+    <row r="315" spans="1:17">
+      <c r="A315" t="s">
+        <v>309</v>
+      </c>
+      <c r="B315">
+        <v>0.026682</v>
+      </c>
+      <c r="C315">
+        <v>2000</v>
+      </c>
+      <c r="D315">
+        <v>0.99</v>
+      </c>
+      <c r="E315">
+        <v>1</v>
+      </c>
+      <c r="F315">
+        <v>1</v>
+      </c>
+      <c r="G315">
+        <v>1</v>
+      </c>
+      <c r="H315">
+        <v>0.5</v>
+      </c>
+      <c r="I315">
+        <v>0</v>
+      </c>
+      <c r="J315">
+        <v>0.5</v>
+      </c>
+      <c r="K315">
+        <v>1</v>
+      </c>
+      <c r="L315">
+        <v>0.5</v>
+      </c>
+      <c r="M315">
+        <v>1</v>
+      </c>
+      <c r="N315">
+        <v>1</v>
+      </c>
+      <c r="O315">
+        <v>1</v>
+      </c>
+      <c r="P315">
+        <v>1</v>
+      </c>
+      <c r="Q315">
+        <v>0.946758910901035</v>
+      </c>
+    </row>
+    <row r="316" spans="1:17">
+      <c r="A316" t="s">
+        <v>310</v>
+      </c>
+      <c r="B316">
+        <v>0.023297</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>0.99</v>
+      </c>
+      <c r="E316">
+        <v>1</v>
+      </c>
+      <c r="F316">
+        <v>1</v>
+      </c>
+      <c r="G316">
+        <v>1</v>
+      </c>
+      <c r="H316">
+        <v>1</v>
+      </c>
+      <c r="I316">
+        <v>0.5</v>
+      </c>
+      <c r="J316">
+        <v>1</v>
+      </c>
+      <c r="K316">
+        <v>1</v>
+      </c>
+      <c r="L316">
+        <v>0.5</v>
+      </c>
+      <c r="M316">
+        <v>1</v>
+      </c>
+      <c r="N316">
+        <v>1</v>
+      </c>
+      <c r="O316">
+        <v>1</v>
+      </c>
+      <c r="P316">
+        <v>1</v>
+      </c>
+      <c r="Q316">
+        <v>0.970909543446185</v>
+      </c>
+    </row>
+    <row r="317" spans="1:17">
+      <c r="A317" t="s">
+        <v>311</v>
+      </c>
+      <c r="B317">
+        <v>0.025133</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>1</v>
+      </c>
+      <c r="E317">
+        <v>1</v>
+      </c>
+      <c r="F317">
+        <v>1</v>
+      </c>
+      <c r="G317">
+        <v>0.5</v>
+      </c>
+      <c r="H317">
+        <v>1</v>
+      </c>
+      <c r="I317">
+        <v>0.5</v>
+      </c>
+      <c r="J317">
+        <v>1</v>
+      </c>
+      <c r="K317">
+        <v>1</v>
+      </c>
+      <c r="L317">
+        <v>0.5</v>
+      </c>
+      <c r="M317">
+        <v>1</v>
+      </c>
+      <c r="N317">
+        <v>1</v>
+      </c>
+      <c r="O317">
+        <v>1</v>
+      </c>
+      <c r="P317">
+        <v>1</v>
+      </c>
+      <c r="Q317">
+        <v>0.967009539594811</v>
+      </c>
+    </row>
+    <row r="318" spans="1:17">
+      <c r="A318" t="s">
+        <v>312</v>
+      </c>
+      <c r="B318">
+        <v>0.027041</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>0.995</v>
+      </c>
+      <c r="E318">
+        <v>1</v>
+      </c>
+      <c r="F318">
+        <v>1</v>
+      </c>
+      <c r="G318">
+        <v>1</v>
+      </c>
+      <c r="H318">
+        <v>1</v>
+      </c>
+      <c r="I318">
+        <v>0.5</v>
+      </c>
+      <c r="J318">
+        <v>1</v>
+      </c>
+      <c r="K318">
+        <v>1</v>
+      </c>
+      <c r="L318">
+        <v>0.5</v>
+      </c>
+      <c r="M318">
+        <v>1</v>
+      </c>
+      <c r="N318">
+        <v>1</v>
+      </c>
+      <c r="O318">
+        <v>1</v>
+      </c>
+      <c r="P318">
+        <v>1</v>
+      </c>
+      <c r="Q318">
+        <v>0.970937804343659</v>
+      </c>
+    </row>
+    <row r="319" spans="1:17">
+      <c r="A319" t="s">
+        <v>313</v>
+      </c>
+      <c r="B319">
+        <v>0.02924</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>0.995</v>
+      </c>
+      <c r="E319">
+        <v>1</v>
+      </c>
+      <c r="F319">
+        <v>1</v>
+      </c>
+      <c r="G319">
+        <v>1</v>
+      </c>
+      <c r="H319">
+        <v>1</v>
+      </c>
+      <c r="I319">
+        <v>0.5</v>
+      </c>
+      <c r="J319">
+        <v>1</v>
+      </c>
+      <c r="K319">
+        <v>1</v>
+      </c>
+      <c r="L319">
+        <v>0.5</v>
+      </c>
+      <c r="M319">
+        <v>1</v>
+      </c>
+      <c r="N319">
+        <v>1</v>
+      </c>
+      <c r="O319">
+        <v>1</v>
+      </c>
+      <c r="P319">
+        <v>1</v>
+      </c>
+      <c r="Q319">
+        <v>0.970937804343659</v>
+      </c>
+    </row>
+    <row r="320" spans="1:17">
+      <c r="A320" t="s">
+        <v>314</v>
+      </c>
+      <c r="B320">
+        <v>0.020317</v>
+      </c>
+      <c r="C320">
+        <v>2000</v>
+      </c>
+      <c r="D320">
+        <v>0.995</v>
+      </c>
+      <c r="E320">
+        <v>1</v>
+      </c>
+      <c r="F320">
+        <v>1</v>
+      </c>
+      <c r="G320">
+        <v>1</v>
+      </c>
+      <c r="H320">
+        <v>1</v>
+      </c>
+      <c r="I320">
+        <v>0.5</v>
+      </c>
+      <c r="J320">
+        <v>1</v>
+      </c>
+      <c r="K320">
+        <v>0.5</v>
+      </c>
+      <c r="L320">
+        <v>1</v>
+      </c>
+      <c r="M320">
+        <v>1</v>
+      </c>
+      <c r="N320">
+        <v>0.5</v>
+      </c>
+      <c r="O320">
+        <v>0.5</v>
+      </c>
+      <c r="P320">
+        <v>0.5</v>
+      </c>
+      <c r="Q320">
+        <v>0.579872323050308</v>
+      </c>
+    </row>
+    <row r="321" spans="1:17">
+      <c r="A321" t="s">
+        <v>315</v>
+      </c>
+      <c r="B321">
+        <v>0.024989</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>0.995</v>
+      </c>
+      <c r="E321">
+        <v>1</v>
+      </c>
+      <c r="F321">
+        <v>1</v>
+      </c>
+      <c r="G321">
+        <v>1</v>
+      </c>
+      <c r="H321">
+        <v>1</v>
+      </c>
+      <c r="I321">
+        <v>1</v>
+      </c>
+      <c r="J321">
+        <v>1</v>
+      </c>
+      <c r="K321">
+        <v>0.5</v>
+      </c>
+      <c r="L321">
+        <v>1</v>
+      </c>
+      <c r="M321">
+        <v>1</v>
+      </c>
+      <c r="N321">
+        <v>0.5</v>
+      </c>
+      <c r="O321">
+        <v>1</v>
+      </c>
+      <c r="P321">
+        <v>0.5</v>
+      </c>
+      <c r="Q321">
+        <v>0.70207145939016</v>
+      </c>
+    </row>
+    <row r="322" spans="1:17">
+      <c r="A322" t="s">
+        <v>316</v>
+      </c>
+      <c r="B322">
+        <v>0.027664</v>
+      </c>
+      <c r="C322">
+        <v>2000</v>
+      </c>
+      <c r="D322">
+        <v>0.995</v>
+      </c>
+      <c r="E322">
+        <v>1</v>
+      </c>
+      <c r="F322">
+        <v>1</v>
+      </c>
+      <c r="G322">
+        <v>1</v>
+      </c>
+      <c r="H322">
+        <v>1</v>
+      </c>
+      <c r="I322">
+        <v>0.5</v>
+      </c>
+      <c r="J322">
+        <v>0.5</v>
+      </c>
+      <c r="K322">
+        <v>0.5</v>
+      </c>
+      <c r="L322">
+        <v>0.5</v>
+      </c>
+      <c r="M322">
+        <v>0.5</v>
+      </c>
+      <c r="N322">
+        <v>0.5</v>
+      </c>
+      <c r="O322">
+        <v>1</v>
+      </c>
+      <c r="P322">
+        <v>1</v>
+      </c>
+      <c r="Q322">
+        <v>0.8567009342720791</v>
+      </c>
+    </row>
+    <row r="323" spans="1:17">
+      <c r="A323" t="s">
+        <v>317</v>
+      </c>
+      <c r="B323">
+        <v>0.023587</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>1</v>
+      </c>
+      <c r="E323">
+        <v>1</v>
+      </c>
+      <c r="F323">
+        <v>1</v>
+      </c>
+      <c r="G323">
+        <v>1</v>
+      </c>
+      <c r="H323">
+        <v>1</v>
+      </c>
+      <c r="I323">
+        <v>0.5</v>
+      </c>
+      <c r="J323">
+        <v>1</v>
+      </c>
+      <c r="K323">
+        <v>1</v>
+      </c>
+      <c r="L323">
+        <v>0.5</v>
+      </c>
+      <c r="M323">
+        <v>1</v>
+      </c>
+      <c r="N323">
+        <v>1</v>
+      </c>
+      <c r="O323">
+        <v>1</v>
+      </c>
+      <c r="P323">
+        <v>1</v>
+      </c>
+      <c r="Q323">
+        <v>0.970966065241133</v>
+      </c>
+    </row>
+    <row r="324" spans="1:17">
+      <c r="A324" t="s">
+        <v>318</v>
+      </c>
+      <c r="B324">
+        <v>0.027379</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>1</v>
+      </c>
+      <c r="E324">
+        <v>1</v>
+      </c>
+      <c r="F324">
+        <v>1</v>
+      </c>
+      <c r="G324">
+        <v>1</v>
+      </c>
+      <c r="H324">
+        <v>1</v>
+      </c>
+      <c r="I324">
+        <v>0.5</v>
+      </c>
+      <c r="J324">
+        <v>1</v>
+      </c>
+      <c r="K324">
+        <v>1</v>
+      </c>
+      <c r="L324">
+        <v>0.5</v>
+      </c>
+      <c r="M324">
+        <v>1</v>
+      </c>
+      <c r="N324">
+        <v>1</v>
+      </c>
+      <c r="O324">
+        <v>1</v>
+      </c>
+      <c r="P324">
+        <v>1</v>
+      </c>
+      <c r="Q324">
+        <v>0.970966065241133</v>
+      </c>
+    </row>
+    <row r="325" spans="1:17">
+      <c r="A325" t="s">
+        <v>319</v>
+      </c>
+      <c r="B325">
+        <v>0.029907</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>1</v>
+      </c>
+      <c r="E325">
+        <v>1</v>
+      </c>
+      <c r="F325">
+        <v>1</v>
+      </c>
+      <c r="G325">
+        <v>1</v>
+      </c>
+      <c r="H325">
+        <v>1</v>
+      </c>
+      <c r="I325">
+        <v>0.5</v>
+      </c>
+      <c r="J325">
+        <v>1</v>
+      </c>
+      <c r="K325">
+        <v>1</v>
+      </c>
+      <c r="L325">
+        <v>0.5</v>
+      </c>
+      <c r="M325">
+        <v>1</v>
+      </c>
+      <c r="N325">
+        <v>1</v>
+      </c>
+      <c r="O325">
+        <v>1</v>
+      </c>
+      <c r="P325">
+        <v>1</v>
+      </c>
+      <c r="Q325">
+        <v>0.970966065241133</v>
+      </c>
+    </row>
+    <row r="326" spans="1:17">
+      <c r="A326" t="s">
+        <v>320</v>
+      </c>
+      <c r="B326">
+        <v>0.027828</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>1</v>
+      </c>
+      <c r="E326">
+        <v>1</v>
+      </c>
+      <c r="F326">
+        <v>1</v>
+      </c>
+      <c r="G326">
+        <v>0.5</v>
+      </c>
+      <c r="H326">
+        <v>1</v>
+      </c>
+      <c r="I326">
+        <v>0.5</v>
+      </c>
+      <c r="J326">
+        <v>1</v>
+      </c>
+      <c r="K326">
+        <v>1</v>
+      </c>
+      <c r="L326">
+        <v>0.5</v>
+      </c>
+      <c r="M326">
+        <v>1</v>
+      </c>
+      <c r="N326">
+        <v>1</v>
+      </c>
+      <c r="O326">
+        <v>1</v>
+      </c>
+      <c r="P326">
+        <v>1</v>
+      </c>
+      <c r="Q326">
+        <v>0.967009539594811</v>
+      </c>
+    </row>
+    <row r="327" spans="1:17">
+      <c r="A327" t="s">
+        <v>321</v>
+      </c>
+      <c r="B327">
+        <v>0.022116</v>
+      </c>
+      <c r="C327">
+        <v>2000</v>
+      </c>
+      <c r="D327">
+        <v>1</v>
+      </c>
+      <c r="E327">
+        <v>1</v>
+      </c>
+      <c r="F327">
+        <v>1</v>
+      </c>
+      <c r="G327">
+        <v>0.5</v>
+      </c>
+      <c r="H327">
+        <v>1</v>
+      </c>
+      <c r="I327">
+        <v>0.5</v>
+      </c>
+      <c r="J327">
+        <v>1</v>
+      </c>
+      <c r="K327">
+        <v>1</v>
+      </c>
+      <c r="L327">
+        <v>0.5</v>
+      </c>
+      <c r="M327">
+        <v>1</v>
+      </c>
+      <c r="N327">
+        <v>1</v>
+      </c>
+      <c r="O327">
+        <v>1</v>
+      </c>
+      <c r="P327">
+        <v>1</v>
+      </c>
+      <c r="Q327">
+        <v>0.967009539594811</v>
+      </c>
+    </row>
+    <row r="328" spans="1:17">
+      <c r="A328" t="s">
+        <v>322</v>
+      </c>
+      <c r="B328">
+        <v>0.026569</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>1</v>
+      </c>
+      <c r="E328">
+        <v>1</v>
+      </c>
+      <c r="F328">
+        <v>1</v>
+      </c>
+      <c r="G328">
+        <v>0.5</v>
+      </c>
+      <c r="H328">
+        <v>1</v>
+      </c>
+      <c r="I328">
+        <v>0.5</v>
+      </c>
+      <c r="J328">
+        <v>1</v>
+      </c>
+      <c r="K328">
+        <v>1</v>
+      </c>
+      <c r="L328">
+        <v>0.5</v>
+      </c>
+      <c r="M328">
+        <v>1</v>
+      </c>
+      <c r="N328">
+        <v>1</v>
+      </c>
+      <c r="O328">
+        <v>1</v>
+      </c>
+      <c r="P328">
+        <v>1</v>
+      </c>
+      <c r="Q328">
+        <v>0.967009539594811</v>
+      </c>
+    </row>
+    <row r="329" spans="1:17">
+      <c r="A329" t="s">
+        <v>323</v>
+      </c>
+      <c r="B329">
+        <v>0.023302</v>
+      </c>
+      <c r="C329">
+        <v>2000</v>
+      </c>
+      <c r="D329">
+        <v>1</v>
+      </c>
+      <c r="E329">
+        <v>1</v>
+      </c>
+      <c r="F329">
+        <v>1</v>
+      </c>
+      <c r="G329">
+        <v>1</v>
+      </c>
+      <c r="H329">
+        <v>1</v>
+      </c>
+      <c r="I329">
+        <v>0.5</v>
+      </c>
+      <c r="J329">
+        <v>1</v>
+      </c>
+      <c r="K329">
+        <v>1</v>
+      </c>
+      <c r="L329">
+        <v>0.5</v>
+      </c>
+      <c r="M329">
+        <v>0.5</v>
+      </c>
+      <c r="N329">
+        <v>1</v>
+      </c>
+      <c r="O329">
+        <v>0.5</v>
+      </c>
+      <c r="P329">
+        <v>0.5</v>
+      </c>
+      <c r="Q329">
+        <v>0.602419998575967</v>
+      </c>
+    </row>
+    <row r="330" spans="1:17">
+      <c r="A330" t="s">
+        <v>324</v>
+      </c>
+      <c r="B330">
+        <v>0.023025</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>0.995</v>
+      </c>
+      <c r="E330">
+        <v>1</v>
+      </c>
+      <c r="F330">
+        <v>1</v>
+      </c>
+      <c r="G330">
+        <v>1</v>
+      </c>
+      <c r="H330">
+        <v>1</v>
+      </c>
+      <c r="I330">
+        <v>0.5</v>
+      </c>
+      <c r="J330">
+        <v>1</v>
+      </c>
+      <c r="K330">
+        <v>1</v>
+      </c>
+      <c r="L330">
+        <v>0.5</v>
+      </c>
+      <c r="M330">
+        <v>1</v>
+      </c>
+      <c r="N330">
+        <v>1</v>
+      </c>
+      <c r="O330">
+        <v>1</v>
+      </c>
+      <c r="P330">
+        <v>1</v>
+      </c>
+      <c r="Q330">
+        <v>0.970937804343659</v>
+      </c>
+    </row>
+    <row r="331" spans="1:17">
+      <c r="A331" t="s">
+        <v>325</v>
+      </c>
+      <c r="B331">
+        <v>0.027274</v>
+      </c>
+      <c r="C331">
+        <v>2000</v>
+      </c>
+      <c r="D331">
+        <v>0.995</v>
+      </c>
+      <c r="E331">
+        <v>1</v>
+      </c>
+      <c r="F331">
+        <v>1</v>
+      </c>
+      <c r="G331">
+        <v>1</v>
+      </c>
+      <c r="H331">
+        <v>1</v>
+      </c>
+      <c r="I331">
+        <v>0.5</v>
+      </c>
+      <c r="J331">
+        <v>1</v>
+      </c>
+      <c r="K331">
+        <v>0.5</v>
+      </c>
+      <c r="L331">
+        <v>0.5</v>
+      </c>
+      <c r="M331">
+        <v>1</v>
+      </c>
+      <c r="N331">
+        <v>1</v>
+      </c>
+      <c r="O331">
+        <v>1</v>
+      </c>
+      <c r="P331">
+        <v>1</v>
+      </c>
+      <c r="Q331">
+        <v>0.955738415420748</v>
+      </c>
+    </row>
+    <row r="332" spans="1:17">
+      <c r="A332" t="s">
+        <v>326</v>
+      </c>
+      <c r="B332">
+        <v>0.027205</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>0.995</v>
+      </c>
+      <c r="E332">
+        <v>1</v>
+      </c>
+      <c r="F332">
+        <v>1</v>
+      </c>
+      <c r="G332">
+        <v>1</v>
+      </c>
+      <c r="H332">
+        <v>0.5</v>
+      </c>
+      <c r="I332">
+        <v>1</v>
+      </c>
+      <c r="J332">
+        <v>1</v>
+      </c>
+      <c r="K332">
+        <v>0.5</v>
+      </c>
+      <c r="L332">
+        <v>1</v>
+      </c>
+      <c r="M332">
+        <v>1</v>
+      </c>
+      <c r="N332">
+        <v>0.5</v>
+      </c>
+      <c r="O332">
+        <v>1</v>
+      </c>
+      <c r="P332">
+        <v>0.5</v>
+      </c>
+      <c r="Q332">
+        <v>0.696532323485309</v>
+      </c>
+    </row>
+    <row r="333" spans="1:17">
+      <c r="A333" t="s">
+        <v>327</v>
+      </c>
+      <c r="B333">
+        <v>0.026171</v>
+      </c>
+      <c r="C333">
+        <v>2000</v>
+      </c>
+      <c r="D333">
+        <v>0.975</v>
+      </c>
+      <c r="E333">
+        <v>1</v>
+      </c>
+      <c r="F333">
+        <v>1</v>
+      </c>
+      <c r="G333">
+        <v>1</v>
+      </c>
+      <c r="H333">
+        <v>1</v>
+      </c>
+      <c r="I333">
+        <v>0.5</v>
+      </c>
+      <c r="J333">
+        <v>0.5</v>
+      </c>
+      <c r="K333">
+        <v>1</v>
+      </c>
+      <c r="L333">
+        <v>0</v>
+      </c>
+      <c r="M333">
+        <v>0.5</v>
+      </c>
+      <c r="N333">
+        <v>1</v>
+      </c>
+      <c r="O333">
+        <v>1</v>
+      </c>
+      <c r="P333">
+        <v>0.5</v>
+      </c>
+      <c r="Q333">
+        <v>0.684587189296076</v>
+      </c>
+    </row>
+    <row r="334" spans="1:17">
+      <c r="A334" t="s">
+        <v>328</v>
+      </c>
+      <c r="B334">
+        <v>0.023772</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>1</v>
+      </c>
+      <c r="E334">
+        <v>1</v>
+      </c>
+      <c r="F334">
+        <v>1</v>
+      </c>
+      <c r="G334">
+        <v>1</v>
+      </c>
+      <c r="H334">
+        <v>1</v>
+      </c>
+      <c r="I334">
+        <v>0.5</v>
+      </c>
+      <c r="J334">
+        <v>1</v>
+      </c>
+      <c r="K334">
+        <v>1</v>
+      </c>
+      <c r="L334">
+        <v>0.5</v>
+      </c>
+      <c r="M334">
+        <v>1</v>
+      </c>
+      <c r="N334">
+        <v>1</v>
+      </c>
+      <c r="O334">
+        <v>1</v>
+      </c>
+      <c r="P334">
+        <v>1</v>
+      </c>
+      <c r="Q334">
+        <v>0.970966065241133</v>
+      </c>
+    </row>
+    <row r="335" spans="1:17">
+      <c r="A335" t="s">
+        <v>329</v>
+      </c>
+      <c r="B335">
+        <v>0.021659</v>
+      </c>
+      <c r="C335">
+        <v>2000</v>
+      </c>
+      <c r="D335">
+        <v>1</v>
+      </c>
+      <c r="E335">
+        <v>1</v>
+      </c>
+      <c r="F335">
+        <v>1</v>
+      </c>
+      <c r="G335">
+        <v>1</v>
+      </c>
+      <c r="H335">
+        <v>1</v>
+      </c>
+      <c r="I335">
+        <v>0.5</v>
+      </c>
+      <c r="J335">
+        <v>1</v>
+      </c>
+      <c r="K335">
+        <v>1</v>
+      </c>
+      <c r="L335">
+        <v>0.5</v>
+      </c>
+      <c r="M335">
+        <v>1</v>
+      </c>
+      <c r="N335">
+        <v>0.5</v>
+      </c>
+      <c r="O335">
+        <v>0.5</v>
+      </c>
+      <c r="P335">
+        <v>0</v>
+      </c>
+      <c r="Q335">
+        <v>0.349509910075418</v>
+      </c>
+    </row>
+    <row r="336" spans="1:17">
+      <c r="A336" t="s">
+        <v>330</v>
+      </c>
+      <c r="B336">
+        <v>0.024222</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>1</v>
+      </c>
+      <c r="E336">
+        <v>1</v>
+      </c>
+      <c r="F336">
+        <v>1</v>
+      </c>
+      <c r="G336">
+        <v>1</v>
+      </c>
+      <c r="H336">
+        <v>1</v>
+      </c>
+      <c r="I336">
+        <v>0.5</v>
+      </c>
+      <c r="J336">
+        <v>1</v>
+      </c>
+      <c r="K336">
+        <v>1</v>
+      </c>
+      <c r="L336">
+        <v>1</v>
+      </c>
+      <c r="M336">
+        <v>1</v>
+      </c>
+      <c r="N336">
+        <v>0.5</v>
+      </c>
+      <c r="O336">
+        <v>1</v>
+      </c>
+      <c r="P336">
+        <v>0</v>
+      </c>
+      <c r="Q336">
+        <v>0.485233400640554</v>
+      </c>
+    </row>
+    <row r="337" spans="1:17">
+      <c r="A337" t="s">
+        <v>331</v>
+      </c>
+      <c r="B337">
+        <v>0.022797</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>1</v>
+      </c>
+      <c r="E337">
+        <v>1</v>
+      </c>
+      <c r="F337">
+        <v>1</v>
+      </c>
+      <c r="G337">
+        <v>1</v>
+      </c>
+      <c r="H337">
+        <v>1</v>
+      </c>
+      <c r="I337">
+        <v>0.5</v>
+      </c>
+      <c r="J337">
+        <v>1</v>
+      </c>
+      <c r="K337">
+        <v>1</v>
+      </c>
+      <c r="L337">
+        <v>1</v>
+      </c>
+      <c r="M337">
+        <v>1</v>
+      </c>
+      <c r="N337">
+        <v>0.5</v>
+      </c>
+      <c r="O337">
+        <v>1</v>
+      </c>
+      <c r="P337">
+        <v>0</v>
+      </c>
+      <c r="Q337">
+        <v>0.485233400640554</v>
+      </c>
+    </row>
+    <row r="338" spans="1:17">
+      <c r="A338" t="s">
+        <v>332</v>
+      </c>
+      <c r="B338">
+        <v>0.024198</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>1</v>
+      </c>
+      <c r="E338">
+        <v>1</v>
+      </c>
+      <c r="F338">
+        <v>1</v>
+      </c>
+      <c r="G338">
+        <v>1</v>
+      </c>
+      <c r="H338">
+        <v>1</v>
+      </c>
+      <c r="I338">
+        <v>0.5</v>
+      </c>
+      <c r="J338">
+        <v>1</v>
+      </c>
+      <c r="K338">
+        <v>1</v>
+      </c>
+      <c r="L338">
+        <v>0.5</v>
+      </c>
+      <c r="M338">
+        <v>1</v>
+      </c>
+      <c r="N338">
+        <v>1</v>
+      </c>
+      <c r="O338">
+        <v>1</v>
+      </c>
+      <c r="P338">
+        <v>1</v>
+      </c>
+      <c r="Q338">
         <v>0.9709660652411329</v>
+      </c>
+    </row>
+    <row r="339" spans="1:17">
+      <c r="A339" t="s">
+        <v>333</v>
+      </c>
+      <c r="B339">
+        <v>0.023811</v>
+      </c>
+      <c r="C339">
+        <v>2000</v>
+      </c>
+      <c r="D339">
+        <v>1</v>
+      </c>
+      <c r="E339">
+        <v>1</v>
+      </c>
+      <c r="F339">
+        <v>1</v>
+      </c>
+      <c r="G339">
+        <v>0.5</v>
+      </c>
+      <c r="H339">
+        <v>0.5</v>
+      </c>
+      <c r="I339">
+        <v>0.5</v>
+      </c>
+      <c r="J339">
+        <v>1</v>
+      </c>
+      <c r="K339">
+        <v>1</v>
+      </c>
+      <c r="L339">
+        <v>0.5</v>
+      </c>
+      <c r="M339">
+        <v>1</v>
+      </c>
+      <c r="N339">
+        <v>0.5</v>
+      </c>
+      <c r="O339">
+        <v>1</v>
+      </c>
+      <c r="P339">
+        <v>0.5</v>
+      </c>
+      <c r="Q339">
+        <v>0.6787695129005048</v>
+      </c>
+    </row>
+    <row r="340" spans="1:17">
+      <c r="A340" t="s">
+        <v>334</v>
+      </c>
+      <c r="B340">
+        <v>0.022075</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>1</v>
+      </c>
+      <c r="E340">
+        <v>1</v>
+      </c>
+      <c r="F340">
+        <v>1</v>
+      </c>
+      <c r="G340">
+        <v>1</v>
+      </c>
+      <c r="H340">
+        <v>1</v>
+      </c>
+      <c r="I340">
+        <v>0.5</v>
+      </c>
+      <c r="J340">
+        <v>1</v>
+      </c>
+      <c r="K340">
+        <v>1</v>
+      </c>
+      <c r="L340">
+        <v>0.5</v>
+      </c>
+      <c r="M340">
+        <v>1</v>
+      </c>
+      <c r="N340">
+        <v>0.5</v>
+      </c>
+      <c r="O340">
+        <v>1</v>
+      </c>
+      <c r="P340">
+        <v>0.5</v>
+      </c>
+      <c r="Q340">
+        <v>0.688265174451678</v>
+      </c>
+    </row>
+    <row r="341" spans="1:17">
+      <c r="A341" t="s">
+        <v>335</v>
+      </c>
+      <c r="B341">
+        <v>0.023175</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0.99</v>
+      </c>
+      <c r="E341">
+        <v>1</v>
+      </c>
+      <c r="F341">
+        <v>1</v>
+      </c>
+      <c r="G341">
+        <v>1</v>
+      </c>
+      <c r="H341">
+        <v>0.5</v>
+      </c>
+      <c r="I341">
+        <v>0.5</v>
+      </c>
+      <c r="J341">
+        <v>1</v>
+      </c>
+      <c r="K341">
+        <v>0.5</v>
+      </c>
+      <c r="L341">
+        <v>0</v>
+      </c>
+      <c r="M341">
+        <v>1</v>
+      </c>
+      <c r="N341">
+        <v>1</v>
+      </c>
+      <c r="O341">
+        <v>1</v>
+      </c>
+      <c r="P341">
+        <v>1</v>
+      </c>
+      <c r="Q341">
+        <v>0.9288918741263475</v>
+      </c>
+    </row>
+    <row r="342" spans="1:17">
+      <c r="A342" t="s">
+        <v>256</v>
+      </c>
+      <c r="B342">
+        <v>0.024846</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0.995</v>
+      </c>
+      <c r="E342">
+        <v>1</v>
+      </c>
+      <c r="F342">
+        <v>1</v>
+      </c>
+      <c r="G342">
+        <v>1</v>
+      </c>
+      <c r="H342">
+        <v>0.5</v>
+      </c>
+      <c r="I342">
+        <v>1</v>
+      </c>
+      <c r="J342">
+        <v>1</v>
+      </c>
+      <c r="K342">
+        <v>1</v>
+      </c>
+      <c r="L342">
+        <v>0.5</v>
+      </c>
+      <c r="M342">
+        <v>1</v>
+      </c>
+      <c r="N342">
+        <v>1</v>
+      </c>
+      <c r="O342">
+        <v>1</v>
+      </c>
+      <c r="P342">
+        <v>1</v>
+      </c>
+      <c r="Q342">
+        <v>0.9731534587055997</v>
+      </c>
+    </row>
+    <row r="343" spans="1:17">
+      <c r="A343" t="s">
+        <v>336</v>
+      </c>
+      <c r="B343">
+        <v>0.021649</v>
+      </c>
+      <c r="C343">
+        <v>2000</v>
+      </c>
+      <c r="D343">
+        <v>1</v>
+      </c>
+      <c r="E343">
+        <v>1</v>
+      </c>
+      <c r="F343">
+        <v>1</v>
+      </c>
+      <c r="G343">
+        <v>0.5</v>
+      </c>
+      <c r="H343">
+        <v>1</v>
+      </c>
+      <c r="I343">
+        <v>0.5</v>
+      </c>
+      <c r="J343">
+        <v>0.5</v>
+      </c>
+      <c r="K343">
+        <v>1</v>
+      </c>
+      <c r="L343">
+        <v>1</v>
+      </c>
+      <c r="M343">
+        <v>0.5</v>
+      </c>
+      <c r="N343">
+        <v>0.5</v>
+      </c>
+      <c r="O343">
+        <v>0.5</v>
+      </c>
+      <c r="P343">
+        <v>0.5</v>
+      </c>
+      <c r="Q343">
+        <v>0.5504959385619568</v>
+      </c>
+    </row>
+    <row r="344" spans="1:17">
+      <c r="A344" t="s">
+        <v>337</v>
+      </c>
+      <c r="B344">
+        <v>0.024348</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>1</v>
+      </c>
+      <c r="E344">
+        <v>1</v>
+      </c>
+      <c r="F344">
+        <v>1</v>
+      </c>
+      <c r="G344">
+        <v>1</v>
+      </c>
+      <c r="H344">
+        <v>1</v>
+      </c>
+      <c r="I344">
+        <v>0.5</v>
+      </c>
+      <c r="J344">
+        <v>1</v>
+      </c>
+      <c r="K344">
+        <v>1</v>
+      </c>
+      <c r="L344">
+        <v>1</v>
+      </c>
+      <c r="M344">
+        <v>1</v>
+      </c>
+      <c r="N344">
+        <v>0.5</v>
+      </c>
+      <c r="O344">
+        <v>1</v>
+      </c>
+      <c r="P344">
+        <v>0.5</v>
+      </c>
+      <c r="Q344">
+        <v>0.7095443189437537</v>
+      </c>
+    </row>
+    <row r="345" spans="1:17">
+      <c r="A345" t="s">
+        <v>338</v>
+      </c>
+      <c r="B345">
+        <v>0.024748</v>
+      </c>
+      <c r="C345">
+        <v>2000</v>
+      </c>
+      <c r="D345">
+        <v>0.995</v>
+      </c>
+      <c r="E345">
+        <v>1</v>
+      </c>
+      <c r="F345">
+        <v>1</v>
+      </c>
+      <c r="G345">
+        <v>0.5</v>
+      </c>
+      <c r="H345">
+        <v>1</v>
+      </c>
+      <c r="I345">
+        <v>0.5</v>
+      </c>
+      <c r="J345">
+        <v>1</v>
+      </c>
+      <c r="K345">
+        <v>0.5</v>
+      </c>
+      <c r="L345">
+        <v>0.5</v>
+      </c>
+      <c r="M345">
+        <v>0.5</v>
+      </c>
+      <c r="N345">
+        <v>1</v>
+      </c>
+      <c r="O345">
+        <v>1</v>
+      </c>
+      <c r="P345">
+        <v>1</v>
+      </c>
+      <c r="Q345">
+        <v>0.9219910874855199</v>
+      </c>
+    </row>
+    <row r="346" spans="1:17">
+      <c r="A346" t="s">
+        <v>339</v>
+      </c>
+      <c r="B346">
+        <v>0.023849</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0.995</v>
+      </c>
+      <c r="E346">
+        <v>1</v>
+      </c>
+      <c r="F346">
+        <v>1</v>
+      </c>
+      <c r="G346">
+        <v>1</v>
+      </c>
+      <c r="H346">
+        <v>1</v>
+      </c>
+      <c r="I346">
+        <v>0.5</v>
+      </c>
+      <c r="J346">
+        <v>1</v>
+      </c>
+      <c r="K346">
+        <v>0.5</v>
+      </c>
+      <c r="L346">
+        <v>1</v>
+      </c>
+      <c r="M346">
+        <v>1</v>
+      </c>
+      <c r="N346">
+        <v>1</v>
+      </c>
+      <c r="O346">
+        <v>1</v>
+      </c>
+      <c r="P346">
+        <v>1</v>
+      </c>
+      <c r="Q346">
+        <v>0.9770175599128236</v>
+      </c>
+    </row>
+    <row r="347" spans="1:17">
+      <c r="A347" t="s">
+        <v>340</v>
+      </c>
+      <c r="B347">
+        <v>0.026486</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0.99</v>
+      </c>
+      <c r="E347">
+        <v>1</v>
+      </c>
+      <c r="F347">
+        <v>1</v>
+      </c>
+      <c r="G347">
+        <v>1</v>
+      </c>
+      <c r="H347">
+        <v>1</v>
+      </c>
+      <c r="I347">
+        <v>0.5</v>
+      </c>
+      <c r="J347">
+        <v>1</v>
+      </c>
+      <c r="K347">
+        <v>1</v>
+      </c>
+      <c r="L347">
+        <v>0.5</v>
+      </c>
+      <c r="M347">
+        <v>1</v>
+      </c>
+      <c r="N347">
+        <v>1</v>
+      </c>
+      <c r="O347">
+        <v>1</v>
+      </c>
+      <c r="P347">
+        <v>1</v>
+      </c>
+      <c r="Q347">
+        <v>0.9709095434461854</v>
+      </c>
+    </row>
+    <row r="348" spans="1:17">
+      <c r="A348" t="s">
+        <v>341</v>
+      </c>
+      <c r="B348">
+        <v>0.020825</v>
+      </c>
+      <c r="C348">
+        <v>2000</v>
+      </c>
+      <c r="D348">
+        <v>1</v>
+      </c>
+      <c r="E348">
+        <v>1</v>
+      </c>
+      <c r="F348">
+        <v>1</v>
+      </c>
+      <c r="G348">
+        <v>1</v>
+      </c>
+      <c r="H348">
+        <v>1</v>
+      </c>
+      <c r="I348">
+        <v>0.5</v>
+      </c>
+      <c r="J348">
+        <v>1</v>
+      </c>
+      <c r="K348">
+        <v>1</v>
+      </c>
+      <c r="L348">
+        <v>0.5</v>
+      </c>
+      <c r="M348">
+        <v>1</v>
+      </c>
+      <c r="N348">
+        <v>1</v>
+      </c>
+      <c r="O348">
+        <v>1</v>
+      </c>
+      <c r="P348">
+        <v>1</v>
+      </c>
+      <c r="Q348">
+        <v>0.9709660652411329</v>
+      </c>
+    </row>
+    <row r="349" spans="1:17">
+      <c r="A349" t="s">
+        <v>342</v>
+      </c>
+      <c r="B349">
+        <v>0.025432</v>
+      </c>
+      <c r="C349">
+        <v>2000</v>
+      </c>
+      <c r="D349">
+        <v>0.98</v>
+      </c>
+      <c r="E349">
+        <v>1</v>
+      </c>
+      <c r="F349">
+        <v>1</v>
+      </c>
+      <c r="G349">
+        <v>1</v>
+      </c>
+      <c r="H349">
+        <v>1</v>
+      </c>
+      <c r="I349">
+        <v>0.5</v>
+      </c>
+      <c r="J349">
+        <v>0.5</v>
+      </c>
+      <c r="K349">
+        <v>0.5</v>
+      </c>
+      <c r="L349">
+        <v>0.5</v>
+      </c>
+      <c r="M349">
+        <v>0</v>
+      </c>
+      <c r="N349">
+        <v>1</v>
+      </c>
+      <c r="O349">
+        <v>0.5</v>
+      </c>
+      <c r="P349">
+        <v>0.5</v>
+      </c>
+      <c r="Q349">
+        <v>0.5464600574007469</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/EVAL_PPO_results.xlsx
+++ b/Code/Jupiter/Connect4/EVAL_PPO_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="348">
   <si>
     <t>TRAINING_SESSION</t>
   </si>
@@ -1043,6 +1043,21 @@
   </si>
   <si>
     <t>PPO-2000-PPO-L-True-SP_FINALE-X_1 - at-2026-04-20 22-02-09</t>
+  </si>
+  <si>
+    <t>PPO_920</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-SOUP_9 - at-2026-04-21 10-52-14</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_851 - at-2026-04-21 15-42-58</t>
+  </si>
+  <si>
+    <t>PPO_853</t>
+  </si>
+  <si>
+    <t>PPO-2000-PPO-L-True-SP_FINALE-PPO_851 - at-2026-04-21 21-12-59</t>
   </si>
 </sst>
 </file>
@@ -1400,7 +1415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q349"/>
+  <dimension ref="A1:Q355"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -19900,6 +19915,324 @@
         <v>0.5464600574007469</v>
       </c>
     </row>
+    <row r="350" spans="1:17">
+      <c r="A350" t="s">
+        <v>343</v>
+      </c>
+      <c r="B350">
+        <v>0.024519</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>1</v>
+      </c>
+      <c r="E350">
+        <v>1</v>
+      </c>
+      <c r="F350">
+        <v>1</v>
+      </c>
+      <c r="G350">
+        <v>1</v>
+      </c>
+      <c r="H350">
+        <v>1</v>
+      </c>
+      <c r="I350">
+        <v>1</v>
+      </c>
+      <c r="J350">
+        <v>1</v>
+      </c>
+      <c r="K350">
+        <v>0.5</v>
+      </c>
+      <c r="L350">
+        <v>1</v>
+      </c>
+      <c r="M350">
+        <v>1</v>
+      </c>
+      <c r="N350">
+        <v>0.5</v>
+      </c>
+      <c r="O350">
+        <v>1</v>
+      </c>
+      <c r="P350">
+        <v>0.5</v>
+      </c>
+      <c r="Q350">
+        <v>0.7020997202876339</v>
+      </c>
+    </row>
+    <row r="351" spans="1:17">
+      <c r="A351" t="s">
+        <v>344</v>
+      </c>
+      <c r="B351">
+        <v>0.021386</v>
+      </c>
+      <c r="C351">
+        <v>2000</v>
+      </c>
+      <c r="D351">
+        <v>0.99</v>
+      </c>
+      <c r="E351">
+        <v>1</v>
+      </c>
+      <c r="F351">
+        <v>1</v>
+      </c>
+      <c r="G351">
+        <v>1</v>
+      </c>
+      <c r="H351">
+        <v>0.5</v>
+      </c>
+      <c r="I351">
+        <v>0.5</v>
+      </c>
+      <c r="J351">
+        <v>1</v>
+      </c>
+      <c r="K351">
+        <v>0.5</v>
+      </c>
+      <c r="L351">
+        <v>0.5</v>
+      </c>
+      <c r="M351">
+        <v>1</v>
+      </c>
+      <c r="N351">
+        <v>0.5</v>
+      </c>
+      <c r="O351">
+        <v>0.5</v>
+      </c>
+      <c r="P351">
+        <v>0.5</v>
+      </c>
+      <c r="Q351">
+        <v>0.5530257817559074</v>
+      </c>
+    </row>
+    <row r="352" spans="1:17">
+      <c r="A352" t="s">
+        <v>345</v>
+      </c>
+      <c r="B352">
+        <v>0.025679</v>
+      </c>
+      <c r="C352">
+        <v>2000</v>
+      </c>
+      <c r="D352">
+        <v>0.985</v>
+      </c>
+      <c r="E352">
+        <v>1</v>
+      </c>
+      <c r="F352">
+        <v>1</v>
+      </c>
+      <c r="G352">
+        <v>0.5</v>
+      </c>
+      <c r="H352">
+        <v>1</v>
+      </c>
+      <c r="I352">
+        <v>0.5</v>
+      </c>
+      <c r="J352">
+        <v>1</v>
+      </c>
+      <c r="K352">
+        <v>0.5</v>
+      </c>
+      <c r="L352">
+        <v>0</v>
+      </c>
+      <c r="M352">
+        <v>0.5</v>
+      </c>
+      <c r="N352">
+        <v>1</v>
+      </c>
+      <c r="O352">
+        <v>1</v>
+      </c>
+      <c r="P352">
+        <v>1</v>
+      </c>
+      <c r="Q352">
+        <v>0.9006554211984968</v>
+      </c>
+    </row>
+    <row r="353" spans="1:17">
+      <c r="A353" t="s">
+        <v>346</v>
+      </c>
+      <c r="B353">
+        <v>0.024491</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0.995</v>
+      </c>
+      <c r="E353">
+        <v>1</v>
+      </c>
+      <c r="F353">
+        <v>1</v>
+      </c>
+      <c r="G353">
+        <v>0.5</v>
+      </c>
+      <c r="H353">
+        <v>1</v>
+      </c>
+      <c r="I353">
+        <v>0.5</v>
+      </c>
+      <c r="J353">
+        <v>1</v>
+      </c>
+      <c r="K353">
+        <v>1</v>
+      </c>
+      <c r="L353">
+        <v>1</v>
+      </c>
+      <c r="M353">
+        <v>1</v>
+      </c>
+      <c r="N353">
+        <v>1</v>
+      </c>
+      <c r="O353">
+        <v>1</v>
+      </c>
+      <c r="P353">
+        <v>1</v>
+      </c>
+      <c r="Q353">
+        <v>0.9882604231894128</v>
+      </c>
+    </row>
+    <row r="354" spans="1:17">
+      <c r="A354" t="s">
+        <v>347</v>
+      </c>
+      <c r="B354">
+        <v>0.026519</v>
+      </c>
+      <c r="C354">
+        <v>2000</v>
+      </c>
+      <c r="D354">
+        <v>1</v>
+      </c>
+      <c r="E354">
+        <v>1</v>
+      </c>
+      <c r="F354">
+        <v>1</v>
+      </c>
+      <c r="G354">
+        <v>1</v>
+      </c>
+      <c r="H354">
+        <v>1</v>
+      </c>
+      <c r="I354">
+        <v>0.5</v>
+      </c>
+      <c r="J354">
+        <v>0.5</v>
+      </c>
+      <c r="K354">
+        <v>0.5</v>
+      </c>
+      <c r="L354">
+        <v>0.5</v>
+      </c>
+      <c r="M354">
+        <v>0.5</v>
+      </c>
+      <c r="N354">
+        <v>1</v>
+      </c>
+      <c r="O354">
+        <v>0.5</v>
+      </c>
+      <c r="P354">
+        <v>0.5</v>
+      </c>
+      <c r="Q354">
+        <v>0.5763639032795477</v>
+      </c>
+    </row>
+    <row r="355" spans="1:17">
+      <c r="A355" t="s">
+        <v>346</v>
+      </c>
+      <c r="B355">
+        <v>0.020848</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0.995</v>
+      </c>
+      <c r="E355">
+        <v>1</v>
+      </c>
+      <c r="F355">
+        <v>1</v>
+      </c>
+      <c r="G355">
+        <v>0.5</v>
+      </c>
+      <c r="H355">
+        <v>0</v>
+      </c>
+      <c r="I355">
+        <v>0</v>
+      </c>
+      <c r="J355">
+        <v>1</v>
+      </c>
+      <c r="K355">
+        <v>1</v>
+      </c>
+      <c r="L355">
+        <v>0.5</v>
+      </c>
+      <c r="M355">
+        <v>1</v>
+      </c>
+      <c r="N355">
+        <v>0.5</v>
+      </c>
+      <c r="O355">
+        <v>1</v>
+      </c>
+      <c r="P355">
+        <v>0</v>
+      </c>
+      <c r="Q355">
+        <v>0.4411364075281894</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Code/Jupiter/Connect4/EVAL_PPO_results.xlsx
+++ b/Code/Jupiter/Connect4/EVAL_PPO_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="21">
   <si>
     <t>TRAINING_SESSION</t>
   </si>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -4889,6 +4889,59 @@
         <v>0.9882604231894128</v>
       </c>
     </row>
+    <row r="85" spans="1:17">
+      <c r="A85" t="s">
+        <v>17</v>
+      </c>
+      <c r="B85">
+        <v>0.024132</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0.995</v>
+      </c>
+      <c r="E85">
+        <v>0.5</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>0.5</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85">
+        <v>1</v>
+      </c>
+      <c r="P85">
+        <v>1</v>
+      </c>
+      <c r="Q85">
+        <v>0.9882604231894128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
